--- a/data/GENKM (TRY).xlsx
+++ b/data/GENKM (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:H108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -412,6 +412,7 @@
     <col min="5" max="5" customWidth="1" width="20"/>
     <col min="6" max="6" customWidth="1" width="20"/>
     <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -419,21 +420,24 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -447,22 +451,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>1115628631</v>
+        <v>1031070183</v>
       </c>
       <c r="C3">
-        <v>352888972</v>
+        <v>1193872145.805984</v>
       </c>
       <c r="D3">
-        <v>252631128.91176966</v>
+        <v>377640878</v>
       </c>
       <c r="E3">
-        <v>519014497.28155565</v>
+        <v>270349164.2204749</v>
       </c>
       <c r="F3">
-        <v>171452515.1045884</v>
+        <v>555415067.6632688</v>
       </c>
       <c r="G3">
-        <v>278092610.4827327</v>
+        <v>183477168.3192378</v>
+      </c>
+      <c r="H3">
+        <v>297596361.7142126</v>
       </c>
     </row>
     <row r="4">
@@ -485,22 +492,25 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>1175027363</v>
+        <v>1214503599</v>
       </c>
       <c r="C7">
-        <v>1142346306</v>
+        <v>1257436749.349217</v>
       </c>
       <c r="D7">
-        <v>997811639.1130235</v>
+        <v>1222471361</v>
       </c>
       <c r="E7">
-        <v>947883553.2335972</v>
+        <v>1067792175.2781293</v>
       </c>
       <c r="F7">
-        <v>883674131.7733952</v>
+        <v>1014362432.2897063</v>
       </c>
       <c r="G7">
-        <v>1122462565.434891</v>
+        <v>945649746.320954</v>
+      </c>
+      <c r="H7">
+        <v>1201185371.4989886</v>
       </c>
     </row>
     <row r="8">
@@ -518,22 +528,25 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>3671776</v>
+        <v>3194334</v>
       </c>
       <c r="C10">
-        <v>2096107</v>
+        <v>3929292.391958084</v>
       </c>
       <c r="D10">
-        <v>2177595.46711176</v>
+        <v>2243130</v>
       </c>
       <c r="E10">
-        <v>8765834.335977143</v>
+        <v>2330318.9796122224</v>
       </c>
       <c r="F10">
-        <v>23079676.38386736</v>
+        <v>9380617.490151886</v>
       </c>
       <c r="G10">
-        <v>57618549.2813906</v>
+        <v>24698346.746638328</v>
+      </c>
+      <c r="H10">
+        <v>61659569.463668264</v>
       </c>
     </row>
     <row r="11">
@@ -556,22 +569,25 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>687889536</v>
+        <v>750809017</v>
       </c>
       <c r="C14">
-        <v>774706820</v>
+        <v>736133990.8296086</v>
       </c>
       <c r="D14">
-        <v>719093766.6252992</v>
+        <v>829045359</v>
       </c>
       <c r="E14">
-        <v>544897762.9181843</v>
+        <v>769526699.424276</v>
       </c>
       <c r="F14">
-        <v>656015704.4721745</v>
+        <v>583113630.6325336</v>
       </c>
       <c r="G14">
-        <v>1262344104.2110436</v>
+        <v>702024719.5328741</v>
+      </c>
+      <c r="H14">
+        <v>1350877364.1718876</v>
       </c>
     </row>
     <row r="15">
@@ -589,22 +605,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>358500229</v>
+        <v>454189302</v>
       </c>
       <c r="C17">
-        <v>222030306</v>
+        <v>383643289.33053946</v>
       </c>
       <c r="D17">
-        <v>252301757.188752</v>
+        <v>237603684</v>
       </c>
       <c r="E17">
-        <v>169695355.68614092</v>
+        <v>269996692.33619344</v>
       </c>
       <c r="F17">
-        <v>211439647.95804626</v>
+        <v>181596772.25630718</v>
       </c>
       <c r="G17">
-        <v>144830481.13020116</v>
+        <v>226268759.33603978</v>
+      </c>
+      <c r="H17">
+        <v>154988024.22275442</v>
       </c>
     </row>
     <row r="18">
@@ -627,22 +646,25 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>31850252</v>
+        <v>20415291</v>
       </c>
       <c r="C21">
-        <v>486018</v>
+        <v>34084038.04195783</v>
       </c>
       <c r="D21">
-        <v>20016255.47859767</v>
+        <v>520107</v>
       </c>
       <c r="E21">
-        <v>3866859.9460025555</v>
+        <v>21420075.834567018</v>
       </c>
       <c r="F21">
-        <v>7975400.082934201</v>
+        <v>4138058.3582972623</v>
       </c>
       <c r="G21">
-        <v>166979335.81862164</v>
+        <v>8534746.909586867</v>
+      </c>
+      <c r="H21">
+        <v>178690267.01147455</v>
       </c>
     </row>
     <row r="22">
@@ -660,22 +682,25 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>3372567787</v>
+        <v>3474181726</v>
       </c>
       <c r="C24">
-        <v>2494554529</v>
+        <v>3609099505.7492647</v>
       </c>
       <c r="D24">
-        <v>2244032142.784554</v>
+        <v>2669524519</v>
       </c>
       <c r="E24">
-        <v>2194123862.3010354</v>
+        <v>2401415126.073253</v>
       </c>
       <c r="F24">
-        <v>1953637075.7750058</v>
+        <v>2348006577.5126657</v>
       </c>
       <c r="G24">
-        <v>3032327646.3588805</v>
+        <v>2090653487.1653306</v>
+      </c>
+      <c r="H24">
+        <v>3244996958.082986</v>
       </c>
     </row>
     <row r="25">
@@ -688,22 +713,25 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>278564613</v>
+        <v>212591441</v>
       </c>
       <c r="C26">
-        <v>325315047</v>
+        <v>298101467.66296417</v>
       </c>
       <c r="D26">
-        <v>315686478.35395163</v>
+        <v>348132897</v>
       </c>
       <c r="E26">
-        <v>203461474.81156674</v>
+        <v>337826838.46733093</v>
       </c>
       <c r="F26">
-        <v>215973593.64958295</v>
+        <v>217731044.87682816</v>
       </c>
       <c r="G26">
-        <v>240747912.27485934</v>
+        <v>231120688.84135446</v>
+      </c>
+      <c r="H26">
+        <v>257632529.89327157</v>
       </c>
     </row>
     <row r="27">
@@ -771,22 +799,25 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>4610208317</v>
+        <v>4887033854</v>
       </c>
       <c r="C39">
-        <v>4603500776</v>
+        <v>4933540734.873256</v>
       </c>
       <c r="D39">
-        <v>4605670096.497531</v>
+        <v>4926393891</v>
       </c>
       <c r="E39">
-        <v>4732025017.547741</v>
+        <v>4928684230.747355</v>
       </c>
       <c r="F39">
-        <v>4308919273.482622</v>
+        <v>5063900929.687883</v>
       </c>
       <c r="G39">
-        <v>2563807830.161429</v>
+        <v>4611121081.148965</v>
+      </c>
+      <c r="H39">
+        <v>2743617966.2092314</v>
       </c>
     </row>
     <row r="40">
@@ -799,33 +830,36 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>3802076</v>
+        <v>4988736</v>
       </c>
       <c r="C41">
-        <v>2294994</v>
+        <v>4068730.854073458</v>
       </c>
       <c r="D41">
-        <v>1775087.4943523807</v>
+        <v>2455966</v>
       </c>
       <c r="E41">
-        <v>1673123.4883817558</v>
+        <v>1899581.5067745822</v>
       </c>
       <c r="F41">
-        <v>907996.7414560015</v>
+        <v>1790466.355710371</v>
       </c>
       <c r="G41">
-        <v>657626.5176628617</v>
+        <v>971678.1982685758</v>
+      </c>
+      <c r="H41">
+        <v>703748.5055195554</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="F42">
-        <v>203336004.69036135</v>
-      </c>
       <c r="G42">
-        <v>9594902.206063401</v>
+        <v>217596775.03229776</v>
+      </c>
+      <c r="H42">
+        <v>10267831.21842584</v>
       </c>
     </row>
     <row r="43">
@@ -853,22 +887,25 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>4892575006</v>
+        <v>5104614031</v>
       </c>
       <c r="C47">
-        <v>4931110817</v>
+        <v>5235710933.390293</v>
       </c>
       <c r="D47">
-        <v>4923131662.345836</v>
+        <v>5276982754</v>
       </c>
       <c r="E47">
-        <v>4937159615.84769</v>
+        <v>5268410650.721462</v>
       </c>
       <c r="F47">
-        <v>4729136868.564022</v>
+        <v>5283422440.920423</v>
       </c>
       <c r="G47">
-        <v>2814808271.1600146</v>
+        <v>5060810223.220885</v>
+      </c>
+      <c r="H47">
+        <v>3012222075.8264484</v>
       </c>
     </row>
     <row r="48">
@@ -876,22 +913,25 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>8265142793</v>
+        <v>8578795757</v>
       </c>
       <c r="C48">
-        <v>7425665346</v>
+        <v>8844810439.139559</v>
       </c>
       <c r="D48">
-        <v>7167163804.029967</v>
+        <v>7946507273</v>
       </c>
       <c r="E48">
-        <v>7131283478.148725</v>
+        <v>7669825775.617116</v>
       </c>
       <c r="F48">
-        <v>6682773944.339028</v>
+        <v>7631429018.433087</v>
       </c>
       <c r="G48">
-        <v>5847135918.619317</v>
+        <v>7151463710.386217</v>
+      </c>
+      <c r="H48">
+        <v>6257219035.087033</v>
       </c>
     </row>
     <row r="49">
@@ -904,22 +944,25 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>410728974</v>
+        <v>236663644</v>
       </c>
       <c r="C50">
-        <v>566886848</v>
+        <v>439535045.90011746</v>
       </c>
       <c r="D50">
-        <v>607545325.6630723</v>
+        <v>606648731</v>
       </c>
       <c r="E50">
-        <v>756115887.1158409</v>
+        <v>650154918.4638733</v>
       </c>
       <c r="F50">
-        <v>276029582.15523624</v>
+        <v>809145329.8575162</v>
       </c>
       <c r="G50">
-        <v>1052055797.0235097</v>
+        <v>295388644.9276695</v>
+      </c>
+      <c r="H50">
+        <v>1125840693.7568836</v>
       </c>
     </row>
     <row r="51">
@@ -932,22 +975,25 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>614824682</v>
+        <v>702691881</v>
       </c>
       <c r="C52">
-        <v>589765545</v>
+        <v>657944805.2851396</v>
       </c>
       <c r="D52">
-        <v>469020722.8087664</v>
+        <v>631132159</v>
       </c>
       <c r="E52">
-        <v>457474313.44661015</v>
+        <v>501915029.0767104</v>
       </c>
       <c r="F52">
-        <v>765610277.8730289</v>
+        <v>489558823.67061967</v>
       </c>
       <c r="G52">
-        <v>619327932.9135455</v>
+        <v>819305600.3556336</v>
+      </c>
+      <c r="H52">
+        <v>662763887.2644521</v>
       </c>
     </row>
     <row r="53">
@@ -960,22 +1006,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>25450481</v>
+        <v>18282420</v>
       </c>
       <c r="C54">
-        <v>23241533</v>
+        <v>27235425.40856898</v>
       </c>
       <c r="D54">
-        <v>14174102.754068876</v>
+        <v>24871713</v>
       </c>
       <c r="E54">
-        <v>20653931.3446428</v>
+        <v>15168189.484978104</v>
       </c>
       <c r="F54">
-        <v>21689863.152677815</v>
+        <v>22102474.469175015</v>
       </c>
       <c r="G54">
-        <v>15144528.638799956</v>
+        <v>23211060.333862666</v>
+      </c>
+      <c r="H54">
+        <v>16206675.232973903</v>
       </c>
     </row>
     <row r="55">
@@ -983,22 +1032,25 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>10088554</v>
+        <v>12611541</v>
       </c>
       <c r="C55">
-        <v>20375030</v>
+        <v>10796104.794534933</v>
       </c>
       <c r="D55">
-        <v>6079115.406164713</v>
+        <v>21804150</v>
       </c>
       <c r="E55">
-        <v>13285302.875131978</v>
+        <v>6505468.175421972</v>
       </c>
       <c r="F55">
-        <v>13494905.76354276</v>
+        <v>14217054.502266735</v>
       </c>
       <c r="G55">
-        <v>48944473.637368485</v>
+        <v>14441357.682734422</v>
+      </c>
+      <c r="H55">
+        <v>52377146.07092181</v>
       </c>
     </row>
     <row r="56">
@@ -1026,22 +1078,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirler</v>
       </c>
       <c r="B60">
-        <v>90264245</v>
+        <v>84536934</v>
       </c>
       <c r="C60">
-        <v>83929011</v>
+        <v>96594838.88568924</v>
       </c>
       <c r="D60">
-        <v>31393229.557712723</v>
+        <v>89815857</v>
       </c>
       <c r="E60">
-        <v>52548265.58963764</v>
+        <v>33594962.78098507</v>
       </c>
       <c r="F60">
-        <v>21007141.510351833</v>
+        <v>56233686.42094614</v>
       </c>
       <c r="G60">
-        <v>36681495.85172474</v>
+        <v>22480456.681837976</v>
+      </c>
+      <c r="H60">
+        <v>39254116.42099737</v>
       </c>
     </row>
     <row r="61">
@@ -1049,16 +1104,19 @@
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
       <c r="B61">
-        <v>27130710</v>
+        <v>34939857</v>
       </c>
       <c r="C61">
-        <v>25438511</v>
+        <v>29033495.613953877</v>
       </c>
       <c r="D61">
-        <v>25784473.046982385</v>
-      </c>
-      <c r="F61">
-        <v>31840650.155685898</v>
+        <v>27222789</v>
+      </c>
+      <c r="E61">
+        <v>27592841.658684015</v>
+      </c>
+      <c r="G61">
+        <v>34073762.78175346</v>
       </c>
     </row>
     <row r="62">
@@ -1066,22 +1124,25 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>5471588</v>
+        <v>6495212</v>
       </c>
       <c r="C62">
-        <v>5304619</v>
+        <v>5855332.433222819</v>
       </c>
       <c r="D62">
-        <v>4666023.847103052</v>
+        <v>5676688</v>
       </c>
       <c r="E62">
-        <v>5766231.306599276</v>
+        <v>4993270.832185028</v>
       </c>
       <c r="F62">
-        <v>3993923.4783244682</v>
+        <v>6170640.257818303</v>
       </c>
       <c r="G62">
-        <v>4199153.289541162</v>
+        <v>4274033.366262839</v>
+      </c>
+      <c r="H62">
+        <v>4493656.768076225</v>
       </c>
     </row>
     <row r="63">
@@ -1089,22 +1150,25 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
-        <v>57600</v>
+        <v>54091</v>
       </c>
       <c r="C63">
-        <v>49269</v>
+        <v>61639.71924670395</v>
       </c>
       <c r="D63">
-        <v>43729.671518866664</v>
+        <v>52725</v>
       </c>
       <c r="E63">
-        <v>3938513.9272539965</v>
+        <v>46796.608943984844</v>
       </c>
       <c r="F63">
-        <v>43580.01412118263</v>
+        <v>4214737.720923086</v>
       </c>
       <c r="G63">
-        <v>49495.883017869186</v>
+        <v>46636.455472171714</v>
+      </c>
+      <c r="H63">
+        <v>52967.228005020115</v>
       </c>
     </row>
     <row r="64">
@@ -1122,22 +1186,25 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>1184016834</v>
+        <v>1096275580</v>
       </c>
       <c r="C66">
-        <v>1314990366</v>
+        <v>1267056688.0404735</v>
       </c>
       <c r="D66">
-        <v>1158706722.7553895</v>
+        <v>1407224812</v>
       </c>
       <c r="E66">
-        <v>1309782444.5052948</v>
+        <v>1239971477.0817819</v>
       </c>
       <c r="F66">
-        <v>1133709923.002547</v>
+        <v>1401642745.721666</v>
       </c>
       <c r="G66">
-        <v>1776402877.2375073</v>
+        <v>1213221551.4076276</v>
+      </c>
+      <c r="H66">
+        <v>1900989142.74231</v>
       </c>
     </row>
     <row r="67">
@@ -1149,11 +1216,11 @@
       <c r="A68" t="str">
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
-      <c r="F68">
-        <v>106808085.80704466</v>
-      </c>
       <c r="G68">
-        <v>165296151.17151174</v>
+        <v>114298965.66708502</v>
+      </c>
+      <c r="H68">
+        <v>176889033.8675819</v>
       </c>
     </row>
     <row r="69">
@@ -1216,22 +1283,25 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>31724935</v>
+        <v>34143763</v>
       </c>
       <c r="C80">
-        <v>23988368</v>
+        <v>33949932.05763771</v>
       </c>
       <c r="D80">
-        <v>25095874.050531182</v>
+        <v>25670931</v>
       </c>
       <c r="E80">
-        <v>23312844.81030317</v>
+        <v>26855948.450093493</v>
       </c>
       <c r="F80">
-        <v>21450327.684308186</v>
+        <v>24947868.210921295</v>
       </c>
       <c r="G80">
-        <v>14901948.302640678</v>
+        <v>22954725.281433295</v>
+      </c>
+      <c r="H80">
+        <v>15947081.763952568</v>
       </c>
     </row>
     <row r="81">
@@ -1244,22 +1314,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>351303165</v>
+        <v>413461955</v>
       </c>
       <c r="C82">
-        <v>305197783</v>
+        <v>375941466.3381686</v>
       </c>
       <c r="D82">
-        <v>297776293.11059314</v>
+        <v>326604592</v>
       </c>
       <c r="E82">
-        <v>293206402.1330613</v>
+        <v>318660540.02884</v>
       </c>
       <c r="F82">
-        <v>245127019.78173923</v>
+        <v>313770144.2503138</v>
       </c>
       <c r="G82">
-        <v>199552271.72581798</v>
+        <v>262318761.7904106</v>
+      </c>
+      <c r="H82">
+        <v>213547673.68439928</v>
       </c>
     </row>
     <row r="83">
@@ -1272,22 +1345,25 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>383028100</v>
+        <v>447605718</v>
       </c>
       <c r="C84">
-        <v>329186151</v>
+        <v>409891398.3958064</v>
       </c>
       <c r="D84">
-        <v>322872168.2615464</v>
+        <v>352275523</v>
       </c>
       <c r="E84">
-        <v>316519246.94336444</v>
+        <v>345516489.6565326</v>
       </c>
       <c r="F84">
-        <v>373385433.27309203</v>
+        <v>338718012.4612351</v>
       </c>
       <c r="G84">
-        <v>379750371.1999704</v>
+        <v>399572452.7389289</v>
+      </c>
+      <c r="H84">
+        <v>406383789.31593376</v>
       </c>
     </row>
     <row r="85">
@@ -1300,22 +1376,25 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>6697968298</v>
+        <v>7034775933</v>
       </c>
       <c r="C86">
-        <v>5781359588</v>
+        <v>7167723705.0702</v>
       </c>
       <c r="D86">
-        <v>5685455524.288935</v>
+        <v>6186868632</v>
       </c>
       <c r="E86">
-        <v>5504853152.86549</v>
+        <v>6084199345.604027</v>
       </c>
       <c r="F86">
-        <v>5174744777.621676</v>
+        <v>5890930604.808366</v>
       </c>
       <c r="G86">
-        <v>3690825996.493217</v>
+        <v>5537670403.922702</v>
+      </c>
+      <c r="H86">
+        <v>3949678441.185386</v>
       </c>
     </row>
     <row r="87">
@@ -1326,10 +1405,10 @@
         <v>609000000</v>
       </c>
       <c r="C87">
+        <v>609000000</v>
+      </c>
+      <c r="D87">
         <v>525000000</v>
-      </c>
-      <c r="D87">
-        <v>547890000</v>
       </c>
       <c r="E87">
         <v>547890000</v>
@@ -1338,6 +1417,9 @@
         <v>547890000</v>
       </c>
       <c r="G87">
+        <v>547890000</v>
+      </c>
+      <c r="H87">
         <v>219156000</v>
       </c>
     </row>
@@ -1346,22 +1428,25 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>2644209361</v>
+        <v>2872391054</v>
       </c>
       <c r="C88">
-        <v>2644209361</v>
+        <v>2872369994.145645</v>
       </c>
       <c r="D88">
-        <v>2621523013.827256</v>
+        <v>2866500164</v>
       </c>
       <c r="E88">
-        <v>2621523013.827256</v>
+        <v>2843806672.728505</v>
       </c>
       <c r="F88">
-        <v>2621523013.827256</v>
+        <v>2843806672.728505</v>
       </c>
       <c r="G88">
-        <v>2013302119.4316807</v>
+        <v>2843806672.728505</v>
+      </c>
+      <c r="H88">
+        <v>2169873369.9964147</v>
       </c>
     </row>
     <row r="89">
@@ -1394,9 +1479,12 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>781288165</v>
+        <v>835188621</v>
       </c>
       <c r="C94">
+        <v>836083040.6488283</v>
+      </c>
+      <c r="D94">
         <v>0</v>
       </c>
     </row>
@@ -1415,22 +1503,25 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>1539347555</v>
+        <v>1646571464</v>
       </c>
       <c r="C97">
-        <v>1540054695</v>
+        <v>1647308179.0503502</v>
       </c>
       <c r="D97">
-        <v>1541148607.4240084</v>
+        <v>1648075325</v>
       </c>
       <c r="E97">
-        <v>1537492720.3918586</v>
+        <v>1649235546.511539</v>
       </c>
       <c r="F97">
-        <v>1354293654.4654186</v>
+        <v>1645323257.4445357</v>
       </c>
       <c r="G97">
-        <v>-6102384.9306604965</v>
+        <v>1449275705.5354357</v>
+      </c>
+      <c r="H97">
+        <v>-6530369.685090798</v>
       </c>
     </row>
     <row r="98">
@@ -1443,22 +1534,25 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>258731067</v>
+        <v>276878665</v>
       </c>
       <c r="C99">
-        <v>258731067</v>
+        <v>276876915.4562526</v>
       </c>
       <c r="D99">
-        <v>258747693.88086072</v>
+        <v>276878665</v>
       </c>
       <c r="E99">
-        <v>258747693.88086072</v>
+        <v>276894708.44702</v>
       </c>
       <c r="F99">
-        <v>258747693.88086072</v>
+        <v>276894708.44702</v>
       </c>
       <c r="G99">
-        <v>239162471.5151898</v>
+        <v>276894708.44702</v>
+      </c>
+      <c r="H99">
+        <v>255935895.8080578</v>
       </c>
     </row>
     <row r="100">
@@ -1481,22 +1575,25 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>813364465</v>
+        <v>870414478</v>
       </c>
       <c r="C103">
-        <v>539165080</v>
+        <v>870408980.344541</v>
       </c>
       <c r="D103">
-        <v>539199723.665093</v>
+        <v>576982536</v>
       </c>
       <c r="E103">
-        <v>393094294.6576908</v>
+        <v>577015965.0107063</v>
       </c>
       <c r="F103">
-        <v>168815128.0949096</v>
+        <v>420663575.69758993</v>
       </c>
       <c r="G103">
-        <v>1169736086.716566</v>
+        <v>180654810.77025333</v>
+      </c>
+      <c r="H103">
+        <v>1251774374.6171403</v>
       </c>
     </row>
     <row r="104">
@@ -1504,22 +1601,25 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>52027685</v>
+        <v>-75668349</v>
       </c>
       <c r="C104">
-        <v>274199385</v>
+        <v>55676595.424582474</v>
       </c>
       <c r="D104">
-        <v>176946484.39129508</v>
+        <v>293431942</v>
       </c>
       <c r="E104">
-        <v>146105429.0074021</v>
+        <v>189356451.72865817</v>
       </c>
       <c r="F104">
-        <v>223475286.25280958</v>
+        <v>156352389.3131163</v>
       </c>
       <c r="G104">
-        <v>55571703.76044077</v>
+        <v>239148505.26388857</v>
+      </c>
+      <c r="H104">
+        <v>59469170.44886408</v>
       </c>
     </row>
     <row r="105">
@@ -1527,22 +1627,25 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B105">
-        <v>129561</v>
+        <v>138526</v>
       </c>
       <c r="C105">
-        <v>129241</v>
+        <v>138647.6330785106</v>
       </c>
       <c r="D105">
-        <v>129389.82451826619</v>
+        <v>138306</v>
       </c>
       <c r="E105">
-        <v>128634.93499759525</v>
+        <v>138464.45237302463</v>
       </c>
       <c r="F105">
-        <v>129931.23216282902</v>
+        <v>137656.6194196143</v>
       </c>
       <c r="G105">
-        <v>156673.6886225159</v>
+        <v>139043.83110928978</v>
+      </c>
+      <c r="H105">
+        <v>167661.84340342702</v>
       </c>
     </row>
     <row r="106">
@@ -1550,22 +1653,25 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>6698097859</v>
+        <v>7034914459</v>
       </c>
       <c r="C106">
-        <v>5781488829</v>
+        <v>7167862352.703279</v>
       </c>
       <c r="D106">
-        <v>5685584914.113453</v>
+        <v>6187006938</v>
       </c>
       <c r="E106">
-        <v>5504981787.8004875</v>
+        <v>6084337810.056399</v>
       </c>
       <c r="F106">
-        <v>5175678589.163811</v>
+        <v>5891068261.427785</v>
       </c>
       <c r="G106">
-        <v>3690982670.1818395</v>
+        <v>5538669707.417258</v>
+      </c>
+      <c r="H106">
+        <v>3949846103.0287895</v>
       </c>
     </row>
     <row r="107">
@@ -1573,39 +1679,48 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>8265142793</v>
+        <v>8578795757</v>
       </c>
       <c r="C107">
-        <v>7425665346</v>
+        <v>8844810439.139559</v>
       </c>
       <c r="D107">
-        <v>7167163804.029967</v>
+        <v>7946507273</v>
       </c>
       <c r="E107">
-        <v>7131283478.148725</v>
+        <v>7669825775.617116</v>
       </c>
       <c r="F107">
-        <v>6682773944.339028</v>
+        <v>7631429018.433087</v>
       </c>
       <c r="G107">
-        <v>5847135918.619317</v>
+        <v>7151463710.386217</v>
+      </c>
+      <c r="H107">
+        <v>6257219035.087033</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
         <v xml:space="preserve">    Hedge Dahil Net Yabancı Para Pozisyonu</v>
       </c>
+      <c r="B108">
+        <v>27175514</v>
+      </c>
+      <c r="C108">
+        <v>26225276.685929235</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1616,6 +1731,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1623,27 +1740,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -1657,28 +1780,34 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1263486134</v>
+        <v>2613562499</v>
       </c>
       <c r="C3">
-        <v>5160691427.47952</v>
+        <v>1352108031</v>
       </c>
       <c r="D3">
-        <v>3739072770.6438484</v>
+        <v>5522631435.915094</v>
       </c>
       <c r="E3">
-        <v>1234203333</v>
+        <v>4001308955.303512</v>
       </c>
       <c r="F3">
-        <v>5462878184.623074</v>
+        <v>2662870914</v>
       </c>
       <c r="G3">
-        <v>4166793218.1733074</v>
+        <v>1320771312</v>
       </c>
       <c r="H3">
-        <v>6241213768.29712</v>
+        <v>5846011763.526216</v>
       </c>
       <c r="I3">
-        <v>8730887247.217728</v>
+        <v>4459027154.987373</v>
+      </c>
+      <c r="J3">
+        <v>6678935146.466973</v>
+      </c>
+      <c r="K3">
+        <v>9343219421.755705</v>
       </c>
     </row>
     <row r="4">
@@ -1701,28 +1830,34 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-897444959</v>
+        <v>-1991242720</v>
       </c>
       <c r="C7">
-        <v>-4046440042.955926</v>
+        <v>-960392444</v>
       </c>
       <c r="D7">
-        <v>-2897083478.6407065</v>
+        <v>-4330233128.410138</v>
       </c>
       <c r="E7">
-        <v>-954781609</v>
+        <v>-3100267573.9180136</v>
       </c>
       <c r="F7">
-        <v>-4403680272.20398</v>
+        <v>-2037876460</v>
       </c>
       <c r="G7">
-        <v>-3293303114.951959</v>
+        <v>-1021750731</v>
       </c>
       <c r="H7">
-        <v>-5028081341.103211</v>
+        <v>-4712528049.147608</v>
       </c>
       <c r="I7">
-        <v>-7340771121.559916</v>
+        <v>-3524275684.026638</v>
+      </c>
+      <c r="J7">
+        <v>-5380720871.791538</v>
+      </c>
+      <c r="K7">
+        <v>-7855608871.306688</v>
       </c>
     </row>
     <row r="8">
@@ -1730,28 +1865,34 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>366041175</v>
+        <v>622319779</v>
       </c>
       <c r="C8">
-        <v>1114251384.5235937</v>
+        <v>391715587</v>
       </c>
       <c r="D8">
-        <v>841989292.0031419</v>
+        <v>1192398307.5049562</v>
       </c>
       <c r="E8">
-        <v>279421724</v>
+        <v>901041381.3854982</v>
       </c>
       <c r="F8">
-        <v>1059197912.4190935</v>
+        <v>624994454</v>
       </c>
       <c r="G8">
-        <v>873490103.2213485</v>
+        <v>299020581</v>
       </c>
       <c r="H8">
-        <v>1213132428.2943308</v>
+        <v>1133483714.3786085</v>
       </c>
       <c r="I8">
-        <v>1390116125.657813</v>
+        <v>934751470.9607357</v>
+      </c>
+      <c r="J8">
+        <v>1298214275.853034</v>
+      </c>
+      <c r="K8">
+        <v>1487610550.4490178</v>
       </c>
     </row>
     <row r="9">
@@ -1779,28 +1920,34 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>366041175</v>
+        <v>622319779</v>
       </c>
       <c r="C13">
-        <v>1114251384.5235937</v>
+        <v>391715587</v>
       </c>
       <c r="D13">
-        <v>841989292.0031419</v>
+        <v>1192398307.5049562</v>
       </c>
       <c r="E13">
-        <v>279421724</v>
+        <v>901041381.3854982</v>
       </c>
       <c r="F13">
-        <v>1059197912.4190935</v>
+        <v>624994454</v>
       </c>
       <c r="G13">
-        <v>873490103.2213485</v>
+        <v>299020581</v>
       </c>
       <c r="H13">
-        <v>1213132428.2943308</v>
+        <v>1133483714.3786085</v>
       </c>
       <c r="I13">
-        <v>1390116125.657813</v>
+        <v>934751470.9607357</v>
+      </c>
+      <c r="J13">
+        <v>1298214275.853034</v>
+      </c>
+      <c r="K13">
+        <v>1487610550.4490178</v>
       </c>
     </row>
     <row r="14"/>
@@ -1809,28 +1956,34 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-45134732</v>
+        <v>-98184742</v>
       </c>
       <c r="C15">
-        <v>-167614342.06079337</v>
+        <v>-48300517</v>
       </c>
       <c r="D15">
-        <v>-134520196.75561133</v>
+        <v>-179369808.7907692</v>
       </c>
       <c r="E15">
-        <v>-44621354</v>
+        <v>-143954638.21227878</v>
       </c>
       <c r="F15">
-        <v>-194219269.9745409</v>
+        <v>-101326302</v>
       </c>
       <c r="G15">
-        <v>-136196691.93712914</v>
+        <v>-47751130</v>
       </c>
       <c r="H15">
-        <v>-191288751.44094688</v>
+        <v>-207840647.1099045</v>
       </c>
       <c r="I15">
-        <v>-140528435.0784861</v>
+        <v>-145748712.73150116</v>
+      </c>
+      <c r="J15">
+        <v>-204704599.5463976</v>
+      </c>
+      <c r="K15">
+        <v>-150384258.4100095</v>
       </c>
     </row>
     <row r="16">
@@ -1838,28 +1991,34 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-61559154</v>
+        <v>-139900406</v>
       </c>
       <c r="C16">
-        <v>-265527417.18921873</v>
+        <v>-65876961</v>
       </c>
       <c r="D16">
-        <v>-198853770.03141266</v>
+        <v>-284149920.96954644</v>
       </c>
       <c r="E16">
-        <v>-64744535</v>
+        <v>-212800183.26189077</v>
       </c>
       <c r="F16">
-        <v>-257585795.66127944</v>
+        <v>-143176001</v>
       </c>
       <c r="G16">
-        <v>-199926996.24286613</v>
+        <v>-69285767</v>
       </c>
       <c r="H16">
-        <v>-340910109.2026911</v>
+        <v>-275651321.640627</v>
       </c>
       <c r="I16">
-        <v>-309700678.7369311</v>
+        <v>-213948679.13623443</v>
+      </c>
+      <c r="J16">
+        <v>-364819503.81279624</v>
+      </c>
+      <c r="K16">
+        <v>-331421230.6919807</v>
       </c>
     </row>
     <row r="17">
@@ -1872,28 +2031,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>19768879</v>
+        <v>56418060</v>
       </c>
       <c r="C18">
-        <v>147719984.73345342</v>
+        <v>21155484</v>
       </c>
       <c r="D18">
-        <v>122969318.57954335</v>
+        <v>158080180.31419206</v>
       </c>
       <c r="E18">
-        <v>42334187</v>
+        <v>131593650.57641576</v>
       </c>
       <c r="F18">
-        <v>113263050.36158423</v>
+        <v>100551110</v>
       </c>
       <c r="G18">
-        <v>93281608.93512282</v>
+        <v>45303540</v>
       </c>
       <c r="H18">
-        <v>458769092.0294262</v>
+        <v>121206642.80057886</v>
       </c>
       <c r="I18">
-        <v>944675712.9395623</v>
+        <v>99823822.66739239</v>
+      </c>
+      <c r="J18">
+        <v>490944410.2735958</v>
+      </c>
+      <c r="K18">
+        <v>1010929613.2773353</v>
       </c>
     </row>
     <row r="19">
@@ -1901,28 +2066,34 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-14197014</v>
+        <v>-44646799</v>
       </c>
       <c r="C19">
-        <v>-124406178.15428573</v>
+        <v>-15192804</v>
       </c>
       <c r="D19">
-        <v>-105108618.21498235</v>
+        <v>-133131282.88169456</v>
       </c>
       <c r="E19">
-        <v>-20920465</v>
+        <v>-112480307.58993931</v>
       </c>
       <c r="F19">
-        <v>-115869064.33885147</v>
+        <v>-70785305</v>
       </c>
       <c r="G19">
-        <v>-96713739.45056021</v>
+        <v>-22387843</v>
       </c>
       <c r="H19">
-        <v>-427852568.60148495</v>
+        <v>-123995427.00043544</v>
       </c>
       <c r="I19">
-        <v>-862877138.9607868</v>
+        <v>-103496662.27485083</v>
+      </c>
+      <c r="J19">
+        <v>-457859586.93709505</v>
+      </c>
+      <c r="K19">
+        <v>-923394176.9087162</v>
       </c>
     </row>
     <row r="20">
@@ -1935,28 +2106,34 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>264919154</v>
+        <v>396005892</v>
       </c>
       <c r="C21">
-        <v>704423431.8527492</v>
+        <v>283500789</v>
       </c>
       <c r="D21">
-        <v>526476025.5806789</v>
+        <v>753827475.1771381</v>
       </c>
       <c r="E21">
-        <v>191469557</v>
+        <v>563399902.8978051</v>
       </c>
       <c r="F21">
-        <v>604786833.906428</v>
+        <v>410257956</v>
       </c>
       <c r="G21">
-        <v>533934283.42549384</v>
+        <v>204899381</v>
       </c>
       <c r="H21">
-        <v>711850089.978212</v>
+        <v>647202962.6058193</v>
       </c>
       <c r="I21">
-        <v>1021685586.9215935</v>
+        <v>571381238.3079426</v>
+      </c>
+      <c r="J21">
+        <v>761774994.6527419</v>
+      </c>
+      <c r="K21">
+        <v>1093340498.893246</v>
       </c>
     </row>
     <row r="22"/>
@@ -1975,28 +2152,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>3458287</v>
+        <v>5613287</v>
       </c>
       <c r="C25">
-        <v>128203850.1648325</v>
+        <v>3700854</v>
       </c>
       <c r="D25">
-        <v>119066102.890124</v>
+        <v>137195300.87685373</v>
       </c>
       <c r="E25">
-        <v>111230163</v>
+        <v>127416686.70045848</v>
       </c>
       <c r="F25">
-        <v>32078290.69729956</v>
+        <v>191122519</v>
       </c>
       <c r="G25">
-        <v>10557463.374461776</v>
+        <v>119031933</v>
       </c>
       <c r="H25">
-        <v>9262019.036310393</v>
+        <v>34328070.0086059</v>
       </c>
       <c r="I25">
-        <v>62385646.89303247</v>
+        <v>11297900.665958047</v>
+      </c>
+      <c r="J25">
+        <v>9911601.615552086</v>
+      </c>
+      <c r="K25">
+        <v>66761002.76928003</v>
       </c>
     </row>
     <row r="26">
@@ -2004,16 +2187,22 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-52935542</v>
-      </c>
-      <c r="E26">
+        <v>-154958212</v>
+      </c>
+      <c r="C26">
+        <v>-56648482</v>
+      </c>
+      <c r="F26">
         <v>0</v>
       </c>
       <c r="G26">
-        <v>-21871199.50010103</v>
-      </c>
-      <c r="H26">
-        <v>-11591247.158671208</v>
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>-23405114.527341653</v>
+      </c>
+      <c r="J26">
+        <v>-12404187.857285557</v>
       </c>
     </row>
     <row r="27">
@@ -2021,33 +2210,39 @@
         <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
       </c>
       <c r="B27">
-        <v>-420090</v>
-      </c>
-      <c r="E27">
-        <v>-1577170</v>
+        <v>-1354361</v>
+      </c>
+      <c r="C27">
+        <v>-449555</v>
+      </c>
+      <c r="F27">
+        <v>-2590321</v>
+      </c>
+      <c r="G27">
+        <v>-1687794</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
-      <c r="C28">
-        <v>-4064716.929539226</v>
-      </c>
       <c r="D28">
-        <v>-2123685.7912842534</v>
-      </c>
-      <c r="F28">
-        <v>-4382308.634599458</v>
-      </c>
-      <c r="G28">
-        <v>-1977356.0698546048</v>
+        <v>-4349791.846425736</v>
+      </c>
+      <c r="E28">
+        <v>-2272628.401787773</v>
       </c>
       <c r="H28">
-        <v>-2363473.2563014566</v>
+        <v>-4689657.532797173</v>
       </c>
       <c r="I28">
-        <v>8452518.870971322</v>
+        <v>-2116035.989524371</v>
+      </c>
+      <c r="J28">
+        <v>-2529233.124401301</v>
+      </c>
+      <c r="K28">
+        <v>9045327.953717697</v>
       </c>
     </row>
     <row r="29">
@@ -2075,28 +2270,34 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>215021809</v>
+        <v>245306606</v>
       </c>
       <c r="C33">
-        <v>828562565.0880425</v>
+        <v>230103606</v>
       </c>
       <c r="D33">
-        <v>643418443.7799406</v>
+        <v>886672984.2075661</v>
       </c>
       <c r="E33">
-        <v>301122550</v>
+        <v>688543962.3740748</v>
       </c>
       <c r="F33">
-        <v>632482814.868706</v>
+        <v>598790154</v>
       </c>
       <c r="G33">
-        <v>520643192.330422</v>
+        <v>322243520</v>
       </c>
       <c r="H33">
-        <v>707157389.6999718</v>
+        <v>676841373.904029</v>
       </c>
       <c r="I33">
-        <v>1092523752.6855974</v>
+        <v>557157989.6346337</v>
+      </c>
+      <c r="J33">
+        <v>756753176.4642062</v>
+      </c>
+      <c r="K33">
+        <v>1169146829.6162438</v>
       </c>
     </row>
     <row r="34"/>
@@ -2105,28 +2306,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>63659596</v>
+        <v>182443113</v>
       </c>
       <c r="C35">
-        <v>177921291.05617452</v>
+        <v>68124729</v>
       </c>
       <c r="D35">
-        <v>151773414.63410997</v>
+        <v>190399625.49850166</v>
       </c>
       <c r="E35">
-        <v>91070377</v>
+        <v>162417893.52708554</v>
       </c>
       <c r="F35">
-        <v>154622723.1214416</v>
+        <v>146644923</v>
       </c>
       <c r="G35">
-        <v>85706098.92091057</v>
+        <v>97458124</v>
       </c>
       <c r="H35">
-        <v>166986355.41082624</v>
+        <v>165467035.45775172</v>
       </c>
       <c r="I35">
-        <v>590172961.7888426</v>
+        <v>91717011.72248548</v>
+      </c>
+      <c r="J35">
+        <v>178697778.91586202</v>
+      </c>
+      <c r="K35">
+        <v>631564160.9663193</v>
       </c>
     </row>
     <row r="36">
@@ -2134,28 +2341,34 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-36513145</v>
+        <v>-83909009</v>
       </c>
       <c r="C36">
-        <v>-268217589.2433983</v>
+        <v>-39074205</v>
       </c>
       <c r="D36">
-        <v>-220653257.22789404</v>
+        <v>-287028765.59011865</v>
       </c>
       <c r="E36">
-        <v>-100145619</v>
+        <v>-236128556.01385656</v>
       </c>
       <c r="F36">
-        <v>-263591847.44555718</v>
+        <v>-184776614</v>
       </c>
       <c r="G36">
-        <v>-215357107.5103746</v>
+        <v>-107169910</v>
       </c>
       <c r="H36">
-        <v>-274384194.8044179</v>
+        <v>-282078601.9490306</v>
       </c>
       <c r="I36">
-        <v>-587669559.9661285</v>
+        <v>-230460966.0541967</v>
+      </c>
+      <c r="J36">
+        <v>-293627859.95620215</v>
+      </c>
+      <c r="K36">
+        <v>-628885185.5233717</v>
       </c>
     </row>
     <row r="37">
@@ -2163,28 +2376,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-80120756</v>
+        <v>-195057243</v>
       </c>
       <c r="C37">
-        <v>-276896317.47181314</v>
+        <v>-85740488</v>
       </c>
       <c r="D37">
-        <v>-252918648.28327173</v>
+        <v>-296316167.87168</v>
       </c>
       <c r="E37">
-        <v>-57625618</v>
+        <v>-270656848.47980434</v>
       </c>
       <c r="F37">
-        <v>-257661926.15939692</v>
+        <v>-238244239</v>
       </c>
       <c r="G37">
-        <v>-254003393.7126587</v>
+        <v>-61667524</v>
       </c>
       <c r="H37">
-        <v>-401424243.01953685</v>
+        <v>-275732791.4762186</v>
       </c>
       <c r="I37">
-        <v>-836750561.2073412</v>
+        <v>-271817671.46108145</v>
+      </c>
+      <c r="J37">
+        <v>-429577736.7802936</v>
+      </c>
+      <c r="K37">
+        <v>-895435237.367057</v>
       </c>
     </row>
     <row r="38">
@@ -2192,28 +2411,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>162047504</v>
+        <v>148783467</v>
       </c>
       <c r="C38">
-        <v>461369949.4290056</v>
+        <v>173413642</v>
       </c>
       <c r="D38">
-        <v>321619952.90288484</v>
+        <v>493727676.2442692</v>
       </c>
       <c r="E38">
-        <v>234421690</v>
+        <v>344176451.40749943</v>
       </c>
       <c r="F38">
-        <v>265851764.38519353</v>
+        <v>322414224</v>
       </c>
       <c r="G38">
-        <v>136988790.02829927</v>
+        <v>250864210</v>
       </c>
       <c r="H38">
-        <v>198335307.28684327</v>
+        <v>284497015.93653154</v>
       </c>
       <c r="I38">
-        <v>258276593.30097017</v>
+        <v>146596363.84184104</v>
+      </c>
+      <c r="J38">
+        <v>212245358.64357248</v>
+      </c>
+      <c r="K38">
+        <v>276390567.6921344</v>
       </c>
     </row>
     <row r="39"/>
@@ -2222,28 +2447,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-110019499</v>
+        <v>-224451596</v>
       </c>
       <c r="C40">
-        <v>-187164875.82244077</v>
+        <v>-117736352</v>
       </c>
       <c r="D40">
-        <v>-144672713.62206912</v>
+        <v>-200291499.97464335</v>
       </c>
       <c r="E40">
-        <v>-101142652</v>
+        <v>-154819191.8458879</v>
       </c>
       <c r="F40">
-        <v>-119747632.77537872</v>
+        <v>-59959847</v>
       </c>
       <c r="G40">
-        <v>-61522642.00717727</v>
+        <v>-108236876</v>
       </c>
       <c r="H40">
-        <v>25113236.509506613</v>
+        <v>-128146015.01270397</v>
       </c>
       <c r="I40">
-        <v>-202650232.6781355</v>
+        <v>-65837471.886074334</v>
+      </c>
+      <c r="J40">
+        <v>26874528.60802193</v>
+      </c>
+      <c r="K40">
+        <v>-216862907.07568583</v>
       </c>
     </row>
     <row r="41">
@@ -2251,28 +2482,34 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-35868580</v>
+        <v>-87946528</v>
       </c>
       <c r="C41">
-        <v>-106427061.37380722</v>
+        <v>-38384430</v>
       </c>
       <c r="D41">
-        <v>-81497653.6676485</v>
+        <v>-113891218.46064596</v>
       </c>
       <c r="E41">
-        <v>-37500399</v>
+        <v>-87213411.30796815</v>
       </c>
       <c r="F41">
-        <v>-28410700.676735338</v>
+        <v>-20838036</v>
       </c>
       <c r="G41">
-        <v>-6190152.391869932</v>
+        <v>-40130706</v>
       </c>
       <c r="H41">
-        <v>-91020106.28732423</v>
+        <v>-30403257.175626878</v>
       </c>
       <c r="I41">
-        <v>-72071593.61714576</v>
+        <v>-6624292.630714853</v>
+      </c>
+      <c r="J41">
+        <v>-97403711.75964963</v>
+      </c>
+      <c r="K41">
+        <v>-77126263.82332301</v>
       </c>
     </row>
     <row r="42">
@@ -2280,28 +2517,34 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-74150919</v>
+        <v>-136505068</v>
       </c>
       <c r="C42">
-        <v>-80737814.44863355</v>
+        <v>-79351922</v>
       </c>
       <c r="D42">
-        <v>-63175059.954420626</v>
+        <v>-86400281.51399739</v>
       </c>
       <c r="E42">
-        <v>-63642253</v>
+        <v>-67605780.53791974</v>
       </c>
       <c r="F42">
-        <v>-91336930.99822134</v>
+        <v>-39121811</v>
       </c>
       <c r="G42">
-        <v>-55332489.61530734</v>
+        <v>-68106170</v>
       </c>
       <c r="H42">
-        <v>116133342.79683085</v>
+        <v>-97742756.65947802</v>
       </c>
       <c r="I42">
-        <v>-130578637.9605677</v>
+        <v>-59213179.255359486</v>
+      </c>
+      <c r="J42">
+        <v>124278240.36767156</v>
+      </c>
+      <c r="K42">
+        <v>-139736642.07476375</v>
       </c>
     </row>
     <row r="43">
@@ -2309,28 +2552,34 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>52028005</v>
+        <v>-75668129</v>
       </c>
       <c r="C43">
-        <v>274205073.6065648</v>
+        <v>55677290</v>
       </c>
       <c r="D43">
-        <v>176947240.38123778</v>
+        <v>293436176.26962584</v>
       </c>
       <c r="E43">
-        <v>133279038</v>
+        <v>189357260.73921064</v>
       </c>
       <c r="F43">
-        <v>146104132.71023685</v>
+        <v>262454377</v>
       </c>
       <c r="G43">
-        <v>75466148.02112201</v>
+        <v>142627334</v>
       </c>
       <c r="H43">
-        <v>223448543.79634988</v>
+        <v>156351002.10142663</v>
       </c>
       <c r="I43">
-        <v>55626360.62283465</v>
+        <v>80758891.95576672</v>
+      </c>
+      <c r="J43">
+        <v>239119887.25159442</v>
+      </c>
+      <c r="K43">
+        <v>59527660.61644854</v>
       </c>
     </row>
     <row r="44">
@@ -2344,28 +2593,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>52028005</v>
+        <v>-75668129</v>
       </c>
       <c r="C46">
-        <v>274205073.6065648</v>
+        <v>55677290</v>
       </c>
       <c r="D46">
-        <v>176947240.38123778</v>
+        <v>293436176.26962584</v>
       </c>
       <c r="E46">
-        <v>133279038</v>
+        <v>189357260.73921064</v>
       </c>
       <c r="F46">
-        <v>146104132.71023685</v>
+        <v>262454377</v>
       </c>
       <c r="G46">
-        <v>75466148.02112201</v>
+        <v>142627334</v>
       </c>
       <c r="H46">
-        <v>223448543.79634988</v>
+        <v>156351002.10142663</v>
       </c>
       <c r="I46">
-        <v>55626360.62283465</v>
+        <v>80758891.95576672</v>
+      </c>
+      <c r="J46">
+        <v>239119887.25159442</v>
+      </c>
+      <c r="K46">
+        <v>59527660.61644854</v>
       </c>
     </row>
     <row r="47">
@@ -2373,28 +2628,34 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="C47">
-        <v>616.2363434048499</v>
+        <v>343</v>
       </c>
       <c r="D47">
-        <v>755.9899427127356</v>
+        <v>659.4554721717082</v>
       </c>
       <c r="E47">
-        <v>34</v>
+        <v>809.0105524677921</v>
       </c>
       <c r="F47">
-        <v>-1296.2971652337735</v>
+        <v>-71</v>
       </c>
       <c r="G47">
-        <v>-1101.5224638361692</v>
+        <v>37</v>
       </c>
       <c r="H47">
-        <v>-26742.4564596869</v>
+        <v>-1387.211689675486</v>
       </c>
       <c r="I47">
-        <v>54656.8623938848</v>
+        <v>-1178.7766565069285</v>
+      </c>
+      <c r="J47">
+        <v>-28618.01229413724</v>
+      </c>
+      <c r="K47">
+        <v>58490.16758445817</v>
       </c>
     </row>
     <row r="48">
@@ -2402,28 +2663,34 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>52027685</v>
+        <v>-75668349</v>
       </c>
       <c r="C48">
-        <v>274204457.37022144</v>
+        <v>55676947</v>
       </c>
       <c r="D48">
-        <v>176946484.39129508</v>
+        <v>293435516.8141537</v>
       </c>
       <c r="E48">
-        <v>133279004</v>
+        <v>189356451.72865817</v>
       </c>
       <c r="F48">
-        <v>146105429.0074021</v>
+        <v>262454448</v>
       </c>
       <c r="G48">
-        <v>75467248.44316381</v>
+        <v>142627297</v>
       </c>
       <c r="H48">
-        <v>223475286.25280958</v>
+        <v>156352389.3131163</v>
       </c>
       <c r="I48">
-        <v>55571703.76044077</v>
+        <v>80760069.55482419</v>
+      </c>
+      <c r="J48">
+        <v>239148505.26388857</v>
+      </c>
+      <c r="K48">
+        <v>59469170.44886408</v>
       </c>
     </row>
     <row r="49"/>
@@ -2432,40 +2699,46 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>27981600</v>
+        <v>60929799</v>
       </c>
       <c r="C50">
-        <v>117170885.62273505</v>
+        <v>29944061.945721723</v>
       </c>
       <c r="D50">
-        <v>87433206.91381867</v>
+        <v>125388550.23737933</v>
       </c>
       <c r="E50">
-        <v>28412774</v>
+        <v>93565248.73275621</v>
       </c>
       <c r="F50">
-        <v>123890710.75851412</v>
+        <v>61589701</v>
       </c>
       <c r="G50">
-        <v>102340505.46842656</v>
+        <v>30405475.90937586</v>
       </c>
       <c r="H50">
-        <v>101116417.99757533</v>
+        <v>132579663.68801068</v>
       </c>
       <c r="I50">
-        <v>100863570.7237661</v>
+        <v>109518055.98332609</v>
+      </c>
+      <c r="J50">
+        <v>108208118.34380044</v>
+      </c>
+      <c r="K50">
+        <v>107937537.8755731</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2476,6 +2749,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2483,27 +2758,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -2517,16 +2798,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1263486134</v>
+        <v>1261454468</v>
       </c>
       <c r="C3">
-        <v>1421618656.8356714</v>
+        <v>1352108031</v>
+      </c>
+      <c r="D3">
+        <v>1521322480.6115823</v>
       </c>
       <c r="E3">
-        <v>1234203333</v>
+        <v>1338438041.303512</v>
       </c>
       <c r="F3">
-        <v>1296084966.4497662</v>
+        <v>1342099602</v>
+      </c>
+      <c r="G3">
+        <v>1320771312</v>
+      </c>
+      <c r="H3">
+        <v>1386984608.5388422</v>
       </c>
     </row>
     <row r="4">
@@ -2549,16 +2839,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-897444959</v>
+        <v>-1030850276</v>
       </c>
       <c r="C7">
-        <v>-1149356564.3152194</v>
+        <v>-960392444</v>
+      </c>
+      <c r="D7">
+        <v>-1229965554.4921246</v>
       </c>
       <c r="E7">
-        <v>-954781609</v>
+        <v>-1062391113.9180136</v>
       </c>
       <c r="F7">
-        <v>-1110377157.2520213</v>
+        <v>-1016125729</v>
+      </c>
+      <c r="G7">
+        <v>-1021750731</v>
+      </c>
+      <c r="H7">
+        <v>-1188252365.1209698</v>
       </c>
     </row>
     <row r="8">
@@ -2566,16 +2865,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>366041175</v>
+        <v>230604192</v>
       </c>
       <c r="C8">
-        <v>272262092.5204518</v>
+        <v>391715587</v>
+      </c>
+      <c r="D8">
+        <v>291356926.1194581</v>
       </c>
       <c r="E8">
-        <v>279421724</v>
+        <v>276046927.38549817</v>
       </c>
       <c r="F8">
-        <v>185707809.19774497</v>
+        <v>325973873</v>
+      </c>
+      <c r="G8">
+        <v>299020581</v>
+      </c>
+      <c r="H8">
+        <v>198732243.4178728</v>
       </c>
     </row>
     <row r="9">
@@ -2603,16 +2911,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>366041175</v>
+        <v>230604192</v>
       </c>
       <c r="C13">
-        <v>272262092.5204518</v>
+        <v>391715587</v>
+      </c>
+      <c r="D13">
+        <v>291356926.1194581</v>
       </c>
       <c r="E13">
-        <v>279421724</v>
+        <v>276046927.38549817</v>
       </c>
       <c r="F13">
-        <v>185707809.19774497</v>
+        <v>325973873</v>
+      </c>
+      <c r="G13">
+        <v>299020581</v>
+      </c>
+      <c r="H13">
+        <v>198732243.4178728</v>
       </c>
     </row>
     <row r="14"/>
@@ -2621,16 +2938,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-45134732</v>
+        <v>-49884225</v>
       </c>
       <c r="C15">
-        <v>-33094145.30518204</v>
+        <v>-48300517</v>
+      </c>
+      <c r="D15">
+        <v>-35415170.57849041</v>
       </c>
       <c r="E15">
-        <v>-44621354</v>
+        <v>-42628336.21227878</v>
       </c>
       <c r="F15">
-        <v>-58022578.03741175</v>
+        <v>-53575172</v>
+      </c>
+      <c r="G15">
+        <v>-47751130</v>
+      </c>
+      <c r="H15">
+        <v>-62091934.378403336</v>
       </c>
     </row>
     <row r="16">
@@ -2638,16 +2964,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-61559154</v>
+        <v>-74023445</v>
       </c>
       <c r="C16">
-        <v>-66673647.15780607</v>
+        <v>-65876961</v>
+      </c>
+      <c r="D16">
+        <v>-71349737.70765567</v>
       </c>
       <c r="E16">
-        <v>-64744535</v>
+        <v>-69624182.26189077</v>
       </c>
       <c r="F16">
-        <v>-57658799.41841331</v>
+        <v>-73890234</v>
+      </c>
+      <c r="G16">
+        <v>-69285767</v>
+      </c>
+      <c r="H16">
+        <v>-61702642.504392594</v>
       </c>
     </row>
     <row r="17">
@@ -2660,16 +2995,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>19768879</v>
+        <v>35262576</v>
       </c>
       <c r="C18">
-        <v>24750666.15391007</v>
+        <v>21155484</v>
+      </c>
+      <c r="D18">
+        <v>26486529.737776294</v>
       </c>
       <c r="E18">
-        <v>42334187</v>
+        <v>31042540.576415762</v>
       </c>
       <c r="F18">
-        <v>19981441.426461414</v>
+        <v>55247570</v>
+      </c>
+      <c r="G18">
+        <v>45303540</v>
+      </c>
+      <c r="H18">
+        <v>21382820.133186474</v>
       </c>
     </row>
     <row r="19">
@@ -2677,16 +3021,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-14197014</v>
+        <v>-29453995</v>
       </c>
       <c r="C19">
-        <v>-19297559.939303383</v>
+        <v>-15192804</v>
+      </c>
+      <c r="D19">
+        <v>-20650975.291755244</v>
       </c>
       <c r="E19">
-        <v>-20920465</v>
+        <v>-41695002.58993931</v>
       </c>
       <c r="F19">
-        <v>-19155324.888291255</v>
+        <v>-48397462</v>
+      </c>
+      <c r="G19">
+        <v>-22387843</v>
+      </c>
+      <c r="H19">
+        <v>-20498764.72558461</v>
       </c>
     </row>
     <row r="20">
@@ -2699,16 +3052,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>264919154</v>
+        <v>112505103</v>
       </c>
       <c r="C21">
-        <v>177947406.27207035</v>
+        <v>283500789</v>
+      </c>
+      <c r="D21">
+        <v>190427572.279333</v>
       </c>
       <c r="E21">
-        <v>191469557</v>
+        <v>153141946.8978051</v>
       </c>
       <c r="F21">
-        <v>70852550.48093414</v>
+        <v>205358575</v>
+      </c>
+      <c r="G21">
+        <v>204899381</v>
+      </c>
+      <c r="H21">
+        <v>75821724.29787672</v>
       </c>
     </row>
     <row r="22"/>
@@ -2727,16 +3089,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>3458287</v>
+        <v>1912433</v>
       </c>
       <c r="C25">
-        <v>9137747.27470851</v>
+        <v>3700854</v>
+      </c>
+      <c r="D25">
+        <v>9778614.176395252</v>
       </c>
       <c r="E25">
-        <v>111230163</v>
+        <v>-63705832.29954152</v>
       </c>
       <c r="F25">
-        <v>21520827.322837785</v>
+        <v>72090586</v>
+      </c>
+      <c r="G25">
+        <v>119031933</v>
+      </c>
+      <c r="H25">
+        <v>23030169.34264785</v>
       </c>
     </row>
     <row r="26">
@@ -2744,9 +3115,15 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
       <c r="B26">
-        <v>-52935542</v>
-      </c>
-      <c r="E26">
+        <v>-98309730</v>
+      </c>
+      <c r="C26">
+        <v>-56648482</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
         <v>0</v>
       </c>
     </row>
@@ -2755,21 +3132,27 @@
         <v xml:space="preserve">    TFRS 9 Uyarınca Belirlenen Değer Düşüklüğü Kazançları (Zararları) ve Değer Düşüklüğü Zararlarının İptalleri</v>
       </c>
       <c r="B27">
-        <v>-420090</v>
-      </c>
-      <c r="E27">
-        <v>-1577170</v>
+        <v>-904806</v>
+      </c>
+      <c r="C27">
+        <v>-449555</v>
+      </c>
+      <c r="F27">
+        <v>-902527</v>
+      </c>
+      <c r="G27">
+        <v>-1687794</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
-      <c r="C28">
-        <v>-1941031.1382549726</v>
-      </c>
-      <c r="F28">
-        <v>-2404952.5647448534</v>
+      <c r="D28">
+        <v>-2077163.4446379635</v>
+      </c>
+      <c r="H28">
+        <v>-2573621.5432728017</v>
       </c>
     </row>
     <row r="29">
@@ -2797,16 +3180,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>215021809</v>
+        <v>15203000</v>
       </c>
       <c r="C33">
-        <v>185144121.3081019</v>
+        <v>230103606</v>
+      </c>
+      <c r="D33">
+        <v>198129021.83349133</v>
       </c>
       <c r="E33">
-        <v>301122550</v>
+        <v>89753808.37407482</v>
       </c>
       <c r="F33">
-        <v>111839622.538284</v>
+        <v>276546634</v>
+      </c>
+      <c r="G33">
+        <v>322243520</v>
+      </c>
+      <c r="H33">
+        <v>119683384.26939535</v>
       </c>
     </row>
     <row r="34"/>
@@ -2815,16 +3207,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>63659596</v>
+        <v>114318384</v>
       </c>
       <c r="C35">
-        <v>26147876.422064543</v>
+        <v>68124729</v>
+      </c>
+      <c r="D35">
+        <v>27981731.971416116</v>
       </c>
       <c r="E35">
-        <v>91070377</v>
+        <v>15772970.527085543</v>
       </c>
       <c r="F35">
-        <v>68916624.20053104</v>
+        <v>49186799</v>
+      </c>
+      <c r="G35">
+        <v>97458124</v>
+      </c>
+      <c r="H35">
+        <v>73750023.73526624</v>
       </c>
     </row>
     <row r="36">
@@ -2832,16 +3233,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-36513145</v>
+        <v>-44834804</v>
       </c>
       <c r="C36">
-        <v>-47564332.01550427</v>
+        <v>-39074205</v>
+      </c>
+      <c r="D36">
+        <v>-50900209.57626209</v>
       </c>
       <c r="E36">
-        <v>-100145619</v>
+        <v>-51351942.01385656</v>
       </c>
       <c r="F36">
-        <v>-48234739.93518257</v>
+        <v>-77606704</v>
+      </c>
+      <c r="G36">
+        <v>-107169910</v>
+      </c>
+      <c r="H36">
+        <v>-51617635.89483389</v>
       </c>
     </row>
     <row r="37">
@@ -2849,16 +3259,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-80120756</v>
+        <v>-109316755</v>
       </c>
       <c r="C37">
-        <v>-23977669.188541412</v>
+        <v>-85740488</v>
+      </c>
+      <c r="D37">
+        <v>-25659319.391875684</v>
       </c>
       <c r="E37">
-        <v>-57625618</v>
+        <v>-32412609.479804337</v>
       </c>
       <c r="F37">
-        <v>-3658532.4467382133</v>
+        <v>-176576715</v>
+      </c>
+      <c r="G37">
+        <v>-61667524</v>
+      </c>
+      <c r="H37">
+        <v>-3915120.015137136</v>
       </c>
     </row>
     <row r="38">
@@ -2866,16 +3285,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>162047504</v>
+        <v>-24630175</v>
       </c>
       <c r="C38">
-        <v>139749996.52612078</v>
+        <v>173413642</v>
+      </c>
+      <c r="D38">
+        <v>149551224.83676976</v>
       </c>
       <c r="E38">
-        <v>234421690</v>
+        <v>21762227.407499433</v>
       </c>
       <c r="F38">
-        <v>128862974.35689425</v>
+        <v>71550014</v>
+      </c>
+      <c r="G38">
+        <v>250864210</v>
+      </c>
+      <c r="H38">
+        <v>137900652.0946905</v>
       </c>
     </row>
     <row r="39"/>
@@ -2884,16 +3312,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-110019499</v>
+        <v>-106715244</v>
       </c>
       <c r="C40">
-        <v>-42492162.20037165</v>
+        <v>-117736352</v>
+      </c>
+      <c r="D40">
+        <v>-45472308.12875545</v>
       </c>
       <c r="E40">
-        <v>-101142652</v>
+        <v>-94859344.8458879</v>
       </c>
       <c r="F40">
-        <v>-58224990.76820145</v>
+        <v>48277029</v>
+      </c>
+      <c r="G40">
+        <v>-108236876</v>
+      </c>
+      <c r="H40">
+        <v>-62308543.126629636</v>
       </c>
     </row>
     <row r="41">
@@ -2901,16 +3338,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-35868580</v>
+        <v>-49562098</v>
       </c>
       <c r="C41">
-        <v>-24929407.706158727</v>
+        <v>-38384430</v>
+      </c>
+      <c r="D41">
+        <v>-26677807.152677804</v>
       </c>
       <c r="E41">
-        <v>-37500399</v>
+        <v>-66375375.307968155</v>
       </c>
       <c r="F41">
-        <v>-22220548.284865405</v>
+        <v>19292670</v>
+      </c>
+      <c r="G41">
+        <v>-40130706</v>
+      </c>
+      <c r="H41">
+        <v>-23778964.544912025</v>
       </c>
     </row>
     <row r="42">
@@ -2918,16 +3364,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-74150919</v>
+        <v>-57153146</v>
       </c>
       <c r="C42">
-        <v>-17562754.494212925</v>
+        <v>-79351922</v>
+      </c>
+      <c r="D42">
+        <v>-18794500.976077646</v>
       </c>
       <c r="E42">
-        <v>-63642253</v>
+        <v>-28483969.537919745</v>
       </c>
       <c r="F42">
-        <v>-36004441.382914</v>
+        <v>28984359</v>
+      </c>
+      <c r="G42">
+        <v>-68106170</v>
+      </c>
+      <c r="H42">
+        <v>-38529577.40411854</v>
       </c>
     </row>
     <row r="43">
@@ -2935,16 +3390,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>52028005</v>
+        <v>-131345419</v>
       </c>
       <c r="C43">
-        <v>97257833.22532704</v>
+        <v>55677290</v>
+      </c>
+      <c r="D43">
+        <v>104078915.5304152</v>
       </c>
       <c r="E43">
-        <v>133279038</v>
+        <v>-73097116.26078936</v>
       </c>
       <c r="F43">
-        <v>70637984.68911484</v>
+        <v>119827043</v>
+      </c>
+      <c r="G43">
+        <v>142627334</v>
+      </c>
+      <c r="H43">
+        <v>75592110.14565991</v>
       </c>
     </row>
     <row r="44">
@@ -2958,16 +3422,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>52028005</v>
+        <v>-131345419</v>
       </c>
       <c r="C46">
-        <v>97257833.22532704</v>
+        <v>55677290</v>
+      </c>
+      <c r="D46">
+        <v>104078915.5304152</v>
       </c>
       <c r="E46">
-        <v>133279038</v>
+        <v>-73097116.26078936</v>
       </c>
       <c r="F46">
-        <v>70637984.68911484</v>
+        <v>119827043</v>
+      </c>
+      <c r="G46">
+        <v>142627334</v>
+      </c>
+      <c r="H46">
+        <v>75592110.14565991</v>
       </c>
     </row>
     <row r="47">
@@ -2975,16 +3448,25 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>320</v>
+        <v>-123</v>
       </c>
       <c r="C47">
-        <v>-139.75359930788568</v>
+        <v>343</v>
+      </c>
+      <c r="D47">
+        <v>-149.55508029608393</v>
       </c>
       <c r="E47">
-        <v>34</v>
+        <v>880.0105524677921</v>
       </c>
       <c r="F47">
-        <v>-194.7747013976043</v>
+        <v>-108</v>
+      </c>
+      <c r="G47">
+        <v>37</v>
+      </c>
+      <c r="H47">
+        <v>-208.43503316855754</v>
       </c>
     </row>
     <row r="48">
@@ -2992,16 +3474,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>52027685</v>
+        <v>-131345296</v>
       </c>
       <c r="C48">
-        <v>97257972.97892636</v>
+        <v>55676947</v>
+      </c>
+      <c r="D48">
+        <v>104079065.0854955</v>
       </c>
       <c r="E48">
-        <v>133279004</v>
+        <v>-73097996.27134183</v>
       </c>
       <c r="F48">
-        <v>70638180.56423828</v>
+        <v>119827151</v>
+      </c>
+      <c r="G48">
+        <v>142627297</v>
+      </c>
+      <c r="H48">
+        <v>75592319.75829212</v>
       </c>
     </row>
     <row r="49"/>
@@ -3010,28 +3501,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>27981600</v>
+        <v>30985737.054278277</v>
       </c>
       <c r="C50">
-        <v>29737678.70891638</v>
+        <v>29944061.945721723</v>
+      </c>
+      <c r="D50">
+        <v>31823301.504623115</v>
       </c>
       <c r="E50">
-        <v>28412774</v>
+        <v>31975547.732756212</v>
       </c>
       <c r="F50">
-        <v>21550205.290087566</v>
+        <v>31184225.09062414</v>
+      </c>
+      <c r="G50">
+        <v>30405475.90937586</v>
+      </c>
+      <c r="H50">
+        <v>23061607.704684585</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:K50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3042,6 +3542,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3049,27 +3551,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3083,22 +3591,25 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>5189974228.47952</v>
+        <v>5473323020.915094</v>
       </c>
       <c r="C3">
-        <v>5160691427.47952</v>
+        <v>5553968154.915094</v>
       </c>
       <c r="D3">
-        <v>5035157737.093615</v>
-      </c>
-      <c r="F3">
-        <v>5462878184.623074</v>
+        <v>5522631435.915094</v>
+      </c>
+      <c r="E3">
+        <v>5388293563.842354</v>
       </c>
       <c r="H3">
-        <v>6241213768.29712</v>
-      </c>
-      <c r="I3">
-        <v>8730887247.217728</v>
+        <v>5846011763.526216</v>
+      </c>
+      <c r="J3">
+        <v>6678935146.466973</v>
+      </c>
+      <c r="K3">
+        <v>9343219421.755705</v>
       </c>
     </row>
     <row r="4">
@@ -3121,22 +3632,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-3989103392.955926</v>
+        <v>-4283599388.410138</v>
       </c>
       <c r="C7">
-        <v>-4046440042.955926</v>
+        <v>-4268874841.410138</v>
       </c>
       <c r="D7">
-        <v>-4007460635.892728</v>
-      </c>
-      <c r="F7">
-        <v>-4403680272.20398</v>
+        <v>-4330233128.410138</v>
+      </c>
+      <c r="E7">
+        <v>-4288519939.0389833</v>
       </c>
       <c r="H7">
-        <v>-5028081341.103211</v>
-      </c>
-      <c r="I7">
-        <v>-7340771121.559916</v>
+        <v>-4712528049.147608</v>
+      </c>
+      <c r="J7">
+        <v>-5380720871.791538</v>
+      </c>
+      <c r="K7">
+        <v>-7855608871.306688</v>
       </c>
     </row>
     <row r="8">
@@ -3144,22 +3658,25 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>1200870835.5235937</v>
+        <v>1189723632.5049562</v>
       </c>
       <c r="C8">
-        <v>1114251384.5235937</v>
+        <v>1285093313.5049562</v>
       </c>
       <c r="D8">
-        <v>1027697101.2008868</v>
-      </c>
-      <c r="F8">
-        <v>1059197912.4190935</v>
+        <v>1192398307.5049562</v>
+      </c>
+      <c r="E8">
+        <v>1099773624.803371</v>
       </c>
       <c r="H8">
-        <v>1213132428.2943308</v>
-      </c>
-      <c r="I8">
-        <v>1390116125.657813</v>
+        <v>1133483714.3786085</v>
+      </c>
+      <c r="J8">
+        <v>1298214275.853034</v>
+      </c>
+      <c r="K8">
+        <v>1487610550.4490178</v>
       </c>
     </row>
     <row r="9">
@@ -3187,22 +3704,25 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>1200870835.5235937</v>
+        <v>1189723632.5049562</v>
       </c>
       <c r="C13">
-        <v>1114251384.5235937</v>
+        <v>1285093313.5049562</v>
       </c>
       <c r="D13">
-        <v>1027697101.2008868</v>
-      </c>
-      <c r="F13">
-        <v>1059197912.4190935</v>
+        <v>1192398307.5049562</v>
+      </c>
+      <c r="E13">
+        <v>1099773624.803371</v>
       </c>
       <c r="H13">
-        <v>1213132428.2943308</v>
-      </c>
-      <c r="I13">
-        <v>1390116125.657813</v>
+        <v>1133483714.3786085</v>
+      </c>
+      <c r="J13">
+        <v>1298214275.853034</v>
+      </c>
+      <c r="K13">
+        <v>1487610550.4490178</v>
       </c>
     </row>
     <row r="14"/>
@@ -3211,22 +3731,25 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-168127720.06079337</v>
+        <v>-176228248.7907692</v>
       </c>
       <c r="C15">
-        <v>-167614342.06079337</v>
+        <v>-179919195.7907692</v>
       </c>
       <c r="D15">
-        <v>-192542774.79302308</v>
-      </c>
-      <c r="F15">
-        <v>-194219269.9745409</v>
+        <v>-179369808.7907692</v>
+      </c>
+      <c r="E15">
+        <v>-206046572.59068212</v>
       </c>
       <c r="H15">
-        <v>-191288751.44094688</v>
-      </c>
-      <c r="I15">
-        <v>-140528435.0784861</v>
+        <v>-207840647.1099045</v>
+      </c>
+      <c r="J15">
+        <v>-204704599.5463976</v>
+      </c>
+      <c r="K15">
+        <v>-150384258.4100095</v>
       </c>
     </row>
     <row r="16">
@@ -3234,22 +3757,25 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-262342036.18921873</v>
+        <v>-280874325.96954644</v>
       </c>
       <c r="C16">
-        <v>-265527417.18921873</v>
+        <v>-280741114.96954644</v>
       </c>
       <c r="D16">
-        <v>-256512569.44982597</v>
-      </c>
-      <c r="F16">
-        <v>-257585795.66127944</v>
+        <v>-284149920.96954644</v>
+      </c>
+      <c r="E16">
+        <v>-274502825.7662834</v>
       </c>
       <c r="H16">
-        <v>-340910109.2026911</v>
-      </c>
-      <c r="I16">
-        <v>-309700678.7369311</v>
+        <v>-275651321.640627</v>
+      </c>
+      <c r="J16">
+        <v>-364819503.81279624</v>
+      </c>
+      <c r="K16">
+        <v>-331421230.6919807</v>
       </c>
     </row>
     <row r="17">
@@ -3262,22 +3788,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>125154676.73345342</v>
+        <v>113947130.31419206</v>
       </c>
       <c r="C18">
-        <v>147719984.73345342</v>
+        <v>133932124.31419206</v>
       </c>
       <c r="D18">
-        <v>142950760.00600475</v>
-      </c>
-      <c r="F18">
-        <v>113263050.36158423</v>
+        <v>158080180.31419206</v>
+      </c>
+      <c r="E18">
+        <v>152976470.70960224</v>
       </c>
       <c r="H18">
-        <v>458769092.0294262</v>
-      </c>
-      <c r="I18">
-        <v>944675712.9395623</v>
+        <v>121206642.80057886</v>
+      </c>
+      <c r="J18">
+        <v>490944410.2735958</v>
+      </c>
+      <c r="K18">
+        <v>1010929613.2773353</v>
       </c>
     </row>
     <row r="19">
@@ -3285,22 +3814,25 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-117682727.15428573</v>
+        <v>-106992776.88169456</v>
       </c>
       <c r="C19">
-        <v>-124406178.15428573</v>
+        <v>-125936243.88169456</v>
       </c>
       <c r="D19">
-        <v>-124263943.1032736</v>
-      </c>
-      <c r="F19">
-        <v>-115869064.33885147</v>
+        <v>-133131282.88169456</v>
+      </c>
+      <c r="E19">
+        <v>-132979072.31552392</v>
       </c>
       <c r="H19">
-        <v>-427852568.60148495</v>
-      </c>
-      <c r="I19">
-        <v>-862877138.9607868</v>
+        <v>-123995427.00043544</v>
+      </c>
+      <c r="J19">
+        <v>-457859586.93709505</v>
+      </c>
+      <c r="K19">
+        <v>-923394176.9087162</v>
       </c>
     </row>
     <row r="20">
@@ -3313,22 +3845,25 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>777873028.8527492</v>
+        <v>739575411.1771381</v>
       </c>
       <c r="C21">
-        <v>704423431.8527492</v>
+        <v>832428883.1771381</v>
       </c>
       <c r="D21">
-        <v>597328576.0616131</v>
-      </c>
-      <c r="F21">
-        <v>604786833.906428</v>
+        <v>753827475.1771381</v>
+      </c>
+      <c r="E21">
+        <v>639221627.1956818</v>
       </c>
       <c r="H21">
-        <v>711850089.978212</v>
-      </c>
-      <c r="I21">
-        <v>1021685586.9215935</v>
+        <v>647202962.6058193</v>
+      </c>
+      <c r="J21">
+        <v>761774994.6527419</v>
+      </c>
+      <c r="K21">
+        <v>1093340498.893246</v>
       </c>
     </row>
     <row r="22"/>
@@ -3347,30 +3882,33 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>20431974.164832503</v>
+        <v>-48313931.123146266</v>
       </c>
       <c r="C25">
-        <v>128203850.1648325</v>
+        <v>21864221.876853734</v>
       </c>
       <c r="D25">
-        <v>140586930.2129618</v>
-      </c>
-      <c r="F25">
-        <v>32078290.69729956</v>
+        <v>137195300.87685373</v>
+      </c>
+      <c r="E25">
+        <v>150446856.04310632</v>
       </c>
       <c r="H25">
-        <v>9262019.036310393</v>
-      </c>
-      <c r="I25">
-        <v>62385646.89303247</v>
+        <v>34328070.0086059</v>
+      </c>
+      <c r="J25">
+        <v>9911601.615552086</v>
+      </c>
+      <c r="K25">
+        <v>66761002.76928003</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
-      <c r="H26">
-        <v>-11591247.158671208</v>
+      <c r="J26">
+        <v>-12404187.857285557</v>
       </c>
     </row>
     <row r="27">
@@ -3382,20 +3920,20 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    Özkaynak Yöntemiyle Değerlenen Yatırımların Karlarından (Zararlarından) Paylar</v>
       </c>
-      <c r="C28">
-        <v>-4064716.929539226</v>
-      </c>
       <c r="D28">
-        <v>-4528638.356029106</v>
-      </c>
-      <c r="F28">
-        <v>-4382308.634599458</v>
+        <v>-4349791.846425736</v>
+      </c>
+      <c r="E28">
+        <v>-4846249.945060574</v>
       </c>
       <c r="H28">
-        <v>-2363473.2563014566</v>
-      </c>
-      <c r="I28">
-        <v>8452518.870971322</v>
+        <v>-4689657.532797173</v>
+      </c>
+      <c r="J28">
+        <v>-2529233.124401301</v>
+      </c>
+      <c r="K28">
+        <v>9045327.953717697</v>
       </c>
     </row>
     <row r="29">
@@ -3423,22 +3961,25 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>742461824.0880425</v>
+        <v>533189436.20756614</v>
       </c>
       <c r="C33">
-        <v>828562565.0880425</v>
+        <v>794533070.2075661</v>
       </c>
       <c r="D33">
-        <v>755258066.3182247</v>
-      </c>
-      <c r="F33">
-        <v>632482814.868706</v>
+        <v>886672984.2075661</v>
+      </c>
+      <c r="E33">
+        <v>808227346.6434702</v>
       </c>
       <c r="H33">
-        <v>707157389.6999718</v>
-      </c>
-      <c r="I33">
-        <v>1092523752.6855974</v>
+        <v>676841373.904029</v>
+      </c>
+      <c r="J33">
+        <v>756753176.4642062</v>
+      </c>
+      <c r="K33">
+        <v>1169146829.6162438</v>
       </c>
     </row>
     <row r="34"/>
@@ -3447,22 +3988,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>150510510.05617452</v>
+        <v>226197815.49850166</v>
       </c>
       <c r="C35">
-        <v>177921291.05617452</v>
+        <v>161066230.49850166</v>
       </c>
       <c r="D35">
-        <v>220690038.834641</v>
-      </c>
-      <c r="F35">
-        <v>154622723.1214416</v>
+        <v>190399625.49850166</v>
+      </c>
+      <c r="E35">
+        <v>236167917.26235178</v>
       </c>
       <c r="H35">
-        <v>166986355.41082624</v>
-      </c>
-      <c r="I35">
-        <v>590172961.7888426</v>
+        <v>165467035.45775172</v>
+      </c>
+      <c r="J35">
+        <v>178697778.91586202</v>
+      </c>
+      <c r="K35">
+        <v>631564160.9663193</v>
       </c>
     </row>
     <row r="36">
@@ -3470,22 +4014,25 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-204585115.2433983</v>
+        <v>-186161160.59011865</v>
       </c>
       <c r="C36">
-        <v>-268217589.2433983</v>
+        <v>-218933060.59011865</v>
       </c>
       <c r="D36">
-        <v>-268887997.16307664</v>
-      </c>
-      <c r="F36">
-        <v>-263591847.44555718</v>
+        <v>-287028765.59011865</v>
+      </c>
+      <c r="E36">
+        <v>-287746191.90869045</v>
       </c>
       <c r="H36">
-        <v>-274384194.8044179</v>
-      </c>
-      <c r="I36">
-        <v>-587669559.9661285</v>
+        <v>-282078601.9490306</v>
+      </c>
+      <c r="J36">
+        <v>-293627859.95620215</v>
+      </c>
+      <c r="K36">
+        <v>-628885185.5233717</v>
       </c>
     </row>
     <row r="37">
@@ -3493,22 +4040,25 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-299391455.47181314</v>
+        <v>-253129171.87168002</v>
       </c>
       <c r="C37">
-        <v>-276896317.47181314</v>
+        <v>-320389131.87168</v>
       </c>
       <c r="D37">
-        <v>-256577180.73000994</v>
-      </c>
-      <c r="F37">
-        <v>-257661926.15939692</v>
+        <v>-296316167.87168</v>
+      </c>
+      <c r="E37">
+        <v>-274571968.4949415</v>
       </c>
       <c r="H37">
-        <v>-401424243.01953685</v>
-      </c>
-      <c r="I37">
-        <v>-836750561.2073412</v>
+        <v>-275732791.4762186</v>
+      </c>
+      <c r="J37">
+        <v>-429577736.7802936</v>
+      </c>
+      <c r="K37">
+        <v>-895435237.367057</v>
       </c>
     </row>
     <row r="38">
@@ -3516,22 +4066,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>388995763.4290056</v>
+        <v>320096919.2442692</v>
       </c>
       <c r="C38">
-        <v>461369949.4290056</v>
+        <v>416277108.2442692</v>
       </c>
       <c r="D38">
-        <v>450482927.2597791</v>
-      </c>
-      <c r="F38">
-        <v>265851764.38519353</v>
+        <v>493727676.2442692</v>
+      </c>
+      <c r="E38">
+        <v>482077103.50218993</v>
       </c>
       <c r="H38">
-        <v>198335307.28684327</v>
-      </c>
-      <c r="I38">
-        <v>258276593.30097017</v>
+        <v>284497015.93653154</v>
+      </c>
+      <c r="J38">
+        <v>212245358.64357248</v>
+      </c>
+      <c r="K38">
+        <v>276390567.6921344</v>
       </c>
     </row>
     <row r="39"/>
@@ -3540,22 +4093,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
       <c r="B40">
-        <v>-196041722.82244077</v>
+        <v>-364783248.97464335</v>
       </c>
       <c r="C40">
-        <v>-187164875.82244077</v>
+        <v>-209790975.97464335</v>
       </c>
       <c r="D40">
-        <v>-202897704.39027056</v>
-      </c>
-      <c r="F40">
-        <v>-119747632.77537872</v>
+        <v>-200291499.97464335</v>
+      </c>
+      <c r="E40">
+        <v>-217127734.97251755</v>
       </c>
       <c r="H40">
-        <v>25113236.509506613</v>
-      </c>
-      <c r="I40">
-        <v>-202650232.6781355</v>
+        <v>-128146015.01270397</v>
+      </c>
+      <c r="J40">
+        <v>26874528.60802193</v>
+      </c>
+      <c r="K40">
+        <v>-216862907.07568583</v>
       </c>
     </row>
     <row r="41">
@@ -3563,22 +4119,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-104795242.37380722</v>
+        <v>-180999710.46064597</v>
       </c>
       <c r="C41">
-        <v>-106427061.37380722</v>
+        <v>-112144942.46064596</v>
       </c>
       <c r="D41">
-        <v>-103718201.9525139</v>
-      </c>
-      <c r="F41">
-        <v>-28410700.676735338</v>
+        <v>-113891218.46064596</v>
+      </c>
+      <c r="E41">
+        <v>-110992375.85288018</v>
       </c>
       <c r="H41">
-        <v>-91020106.28732423</v>
-      </c>
-      <c r="I41">
-        <v>-72071593.61714576</v>
+        <v>-30403257.175626878</v>
+      </c>
+      <c r="J41">
+        <v>-97403711.75964963</v>
+      </c>
+      <c r="K41">
+        <v>-77126263.82332301</v>
       </c>
     </row>
     <row r="42">
@@ -3586,22 +4145,25 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-91246480.44863355</v>
+        <v>-183783538.51399738</v>
       </c>
       <c r="C42">
-        <v>-80737814.44863355</v>
+        <v>-97646033.51399739</v>
       </c>
       <c r="D42">
-        <v>-99179501.33733463</v>
-      </c>
-      <c r="F42">
-        <v>-91336930.99822134</v>
+        <v>-86400281.51399739</v>
+      </c>
+      <c r="E42">
+        <v>-106135357.94203828</v>
       </c>
       <c r="H42">
-        <v>116133342.79683085</v>
-      </c>
-      <c r="I42">
-        <v>-130578637.9605677</v>
+        <v>-97742756.65947802</v>
+      </c>
+      <c r="J42">
+        <v>124278240.36767156</v>
+      </c>
+      <c r="K42">
+        <v>-139736642.07476375</v>
       </c>
     </row>
     <row r="43">
@@ -3609,22 +4171,25 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>192954040.60656482</v>
+        <v>-44686329.73037416</v>
       </c>
       <c r="C43">
-        <v>274205073.6065648</v>
+        <v>206486132.26962584</v>
       </c>
       <c r="D43">
-        <v>247585225.0703526</v>
-      </c>
-      <c r="F43">
-        <v>146104132.71023685</v>
+        <v>293436176.26962584</v>
+      </c>
+      <c r="E43">
+        <v>264949370.88487053</v>
       </c>
       <c r="H43">
-        <v>223448543.79634988</v>
-      </c>
-      <c r="I43">
-        <v>55626360.62283465</v>
+        <v>156351002.10142663</v>
+      </c>
+      <c r="J43">
+        <v>239119887.25159442</v>
+      </c>
+      <c r="K43">
+        <v>59527660.61644854</v>
       </c>
     </row>
     <row r="44">
@@ -3638,22 +4203,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>192954040.60656482</v>
+        <v>-44686329.73037416</v>
       </c>
       <c r="C46">
-        <v>274205073.6065648</v>
+        <v>206486132.26962584</v>
       </c>
       <c r="D46">
-        <v>247585225.0703526</v>
-      </c>
-      <c r="F46">
-        <v>146104132.71023685</v>
+        <v>293436176.26962584</v>
+      </c>
+      <c r="E46">
+        <v>264949370.88487053</v>
       </c>
       <c r="H46">
-        <v>223448543.79634988</v>
-      </c>
-      <c r="I46">
-        <v>55626360.62283465</v>
+        <v>156351002.10142663</v>
+      </c>
+      <c r="J46">
+        <v>239119887.25159442</v>
+      </c>
+      <c r="K46">
+        <v>59527660.61644854</v>
       </c>
     </row>
     <row r="47">
@@ -3661,22 +4229,25 @@
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
       <c r="B47">
-        <v>902.2363434048499</v>
+        <v>950.4554721717082</v>
       </c>
       <c r="C47">
-        <v>616.2363434048499</v>
+        <v>965.4554721717082</v>
       </c>
       <c r="D47">
-        <v>561.2152413151313</v>
-      </c>
-      <c r="F47">
-        <v>-1296.2971652337735</v>
+        <v>659.4554721717082</v>
+      </c>
+      <c r="E47">
+        <v>600.5755192992345</v>
       </c>
       <c r="H47">
-        <v>-26742.4564596869</v>
-      </c>
-      <c r="I47">
-        <v>54656.8623938848</v>
+        <v>-1387.211689675486</v>
+      </c>
+      <c r="J47">
+        <v>-28618.01229413724</v>
+      </c>
+      <c r="K47">
+        <v>58490.16758445817</v>
       </c>
     </row>
     <row r="48">
@@ -3684,22 +4255,25 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>192953138.37022144</v>
+        <v>-44687280.18584633</v>
       </c>
       <c r="C48">
-        <v>274204457.37022144</v>
+        <v>206485166.81415367</v>
       </c>
       <c r="D48">
-        <v>247584664.95553336</v>
-      </c>
-      <c r="F48">
-        <v>146105429.0074021</v>
+        <v>293435516.8141537</v>
+      </c>
+      <c r="E48">
+        <v>264948771.48695028</v>
       </c>
       <c r="H48">
-        <v>223475286.25280958</v>
-      </c>
-      <c r="I48">
-        <v>55571703.76044077</v>
+        <v>156352389.3131163</v>
+      </c>
+      <c r="J48">
+        <v>239148505.26388857</v>
+      </c>
+      <c r="K48">
+        <v>59469170.44886408</v>
       </c>
     </row>
     <row r="49"/>
@@ -3708,34 +4282,37 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>116739711.62273505</v>
+        <v>124728648.23737933</v>
       </c>
       <c r="C50">
-        <v>117170885.62273505</v>
+        <v>124927136.27372518</v>
       </c>
       <c r="D50">
-        <v>108983412.20390624</v>
-      </c>
-      <c r="F50">
-        <v>123890710.75851412</v>
+        <v>125388550.23737933</v>
+      </c>
+      <c r="E50">
+        <v>116626856.4374408</v>
       </c>
       <c r="H50">
-        <v>101116417.99757533</v>
-      </c>
-      <c r="I50">
-        <v>100863570.7237661</v>
+        <v>132579663.68801068</v>
+      </c>
+      <c r="J50">
+        <v>108208118.34380044</v>
+      </c>
+      <c r="K50">
+        <v>107937537.8755731</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3746,6 +4323,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3753,27 +4332,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -3787,28 +4372,34 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>181830884</v>
+        <v>174276606</v>
       </c>
       <c r="C3">
-        <v>211985197.5911744</v>
+        <v>194583413.89131933</v>
       </c>
       <c r="D3">
-        <v>17386761.796224676</v>
+        <v>136863817.34057322</v>
       </c>
       <c r="E3">
-        <v>35337141</v>
+        <v>18606165.203621652</v>
       </c>
       <c r="F3">
-        <v>139762683.2918406</v>
+        <v>-8410049</v>
       </c>
       <c r="G3">
-        <v>-66189394.333671995</v>
+        <v>37815476.566340126</v>
       </c>
       <c r="H3">
-        <v>1330559689.143941</v>
+        <v>118687280.3114771</v>
       </c>
       <c r="I3">
-        <v>1149481746.12585</v>
+        <v>-77605764.49553058</v>
+      </c>
+      <c r="J3">
+        <v>1423877181.9412189</v>
+      </c>
+      <c r="K3">
+        <v>1195585577.094665</v>
       </c>
     </row>
     <row r="4">
@@ -3816,28 +4407,34 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>52028005</v>
+        <v>-75668129</v>
       </c>
       <c r="C4">
-        <v>274205073.6065648</v>
+        <v>55676937.86746718</v>
       </c>
       <c r="D4">
-        <v>176947240.38123778</v>
+        <v>293436176.26962584</v>
       </c>
       <c r="E4">
-        <v>133279038</v>
+        <v>189357260.73921064</v>
       </c>
       <c r="F4">
-        <v>146104132.71023685</v>
+        <v>262454377</v>
       </c>
       <c r="G4">
-        <v>75466148.02112201</v>
+        <v>142626432.0102567</v>
       </c>
       <c r="H4">
-        <v>223448543.79634988</v>
+        <v>156351002.10142663</v>
       </c>
       <c r="I4">
-        <v>55626360.62283465</v>
+        <v>80758891.95576672</v>
+      </c>
+      <c r="J4">
+        <v>239119887.25159442</v>
+      </c>
+      <c r="K4">
+        <v>59527660.61644854</v>
       </c>
     </row>
     <row r="5">
@@ -3845,28 +4442,34 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>214418633</v>
+        <v>390585365</v>
       </c>
       <c r="C5">
-        <v>234388462.15270343</v>
+        <v>229456672.55871615</v>
       </c>
       <c r="D5">
-        <v>172168440.88160348</v>
+        <v>250827066.00276622</v>
       </c>
       <c r="E5">
-        <v>166212925</v>
+        <v>184243304.84522197</v>
       </c>
       <c r="F5">
-        <v>154202894.50574437</v>
+        <v>114408274</v>
       </c>
       <c r="G5">
-        <v>146373106.66906857</v>
+        <v>177870104.72523367</v>
       </c>
       <c r="H5">
-        <v>-9895550.712946124</v>
+        <v>165017762.5757498</v>
       </c>
       <c r="I5">
-        <v>-590830131.631358</v>
+        <v>156638840.28384092</v>
+      </c>
+      <c r="J5">
+        <v>-10589565.412109725</v>
+      </c>
+      <c r="K5">
+        <v>-632267420.76823</v>
       </c>
     </row>
     <row r="6">
@@ -3874,28 +4477,34 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>27981600</v>
+        <v>60929799</v>
       </c>
       <c r="C6">
-        <v>117170885.62273505</v>
+        <v>29944061.945721723</v>
       </c>
       <c r="D6">
-        <v>87433206.91381867</v>
+        <v>125388550.23737933</v>
       </c>
       <c r="E6">
-        <v>28412774</v>
+        <v>93565248.73275621</v>
       </c>
       <c r="F6">
-        <v>123890710.75851412</v>
+        <v>61589701</v>
       </c>
       <c r="G6">
-        <v>102340505.46842656</v>
+        <v>30405475.90937586</v>
       </c>
       <c r="H6">
-        <v>101116417.99757533</v>
+        <v>132579663.68801068</v>
       </c>
       <c r="I6">
-        <v>100863570.7237661</v>
+        <v>109518055.98332609</v>
+      </c>
+      <c r="J6">
+        <v>108208118.34380044</v>
+      </c>
+      <c r="K6">
+        <v>107937537.8755731</v>
       </c>
     </row>
     <row r="7">
@@ -3903,28 +4512,34 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-3235692</v>
+        <v>-5439413</v>
       </c>
       <c r="C7">
-        <v>5112180.060150205</v>
+        <v>-3462624.0702917706</v>
       </c>
       <c r="D7">
-        <v>563843.0491509362</v>
+        <v>5470717.771636402</v>
       </c>
       <c r="E7">
-        <v>-1633167</v>
+        <v>603387.6258484237</v>
       </c>
       <c r="F7">
-        <v>-13799743.577138597</v>
+        <v>-2779733</v>
       </c>
       <c r="G7">
-        <v>-14277717.393102191</v>
+        <v>-1747707.5583850998</v>
       </c>
       <c r="H7">
-        <v>-12622041.096193086</v>
+        <v>-14767574.996030021</v>
       </c>
       <c r="I7">
-        <v>80923624.01165666</v>
+        <v>-15279071.034628488</v>
+      </c>
+      <c r="J7">
+        <v>-13507275.511973979</v>
+      </c>
+      <c r="K7">
+        <v>86599122.6476449</v>
       </c>
     </row>
     <row r="8">
@@ -3932,28 +4547,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>7196396</v>
+        <v>7787495</v>
       </c>
       <c r="C8">
-        <v>4117154.2406748114</v>
+        <v>7701108.142849016</v>
       </c>
       <c r="D8">
-        <v>4338708.812881524</v>
+        <v>4405906.796711319</v>
       </c>
       <c r="E8">
-        <v>6961942</v>
+        <v>4642999.880541967</v>
       </c>
       <c r="F8">
-        <v>3732316.8450625665</v>
+        <v>4716784</v>
       </c>
       <c r="G8">
-        <v>3234950.2914564284</v>
+        <v>7450210.942566607</v>
       </c>
       <c r="H8">
-        <v>-7472352.050326278</v>
+        <v>3994079.2095382023</v>
       </c>
       <c r="I8">
-        <v>-2638848.37015029</v>
+        <v>3461830.3427503016</v>
+      </c>
+      <c r="J8">
+        <v>-7996418.098865354</v>
+      </c>
+      <c r="K8">
+        <v>-2823921.400532746</v>
       </c>
     </row>
     <row r="9">
@@ -3976,28 +4597,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-28299314</v>
+        <v>-100381885</v>
       </c>
       <c r="C12">
-        <v>54391626.568729065</v>
+        <v>-30284058.504068032</v>
       </c>
       <c r="D12">
-        <v>35378845.950043686</v>
+        <v>58206329.706042066</v>
       </c>
       <c r="E12">
-        <v>-12079086</v>
+        <v>37860106.45196322</v>
       </c>
       <c r="F12">
-        <v>59585830.98745258</v>
+        <v>3404747</v>
       </c>
       <c r="G12">
-        <v>61290211.96393151</v>
+        <v>-12926240.795083199</v>
       </c>
       <c r="H12">
-        <v>163987922.1300788</v>
+        <v>63764824.533821695</v>
       </c>
       <c r="I12">
-        <v>218999425.23832697</v>
+        <v>65588740.59075892</v>
+      </c>
+      <c r="J12">
+        <v>175489053.4713265</v>
+      </c>
+      <c r="K12">
+        <v>234358734.1472223</v>
       </c>
     </row>
     <row r="13">
@@ -4030,28 +4657,34 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
-        <v>52935542</v>
+        <v>140346074</v>
       </c>
       <c r="C18">
-        <v>-121318689.91853996</v>
+        <v>56648124.08076572</v>
       </c>
       <c r="D18">
-        <v>-112225003.5423849</v>
+        <v>-129827256.70063777</v>
       </c>
       <c r="E18">
-        <v>-111230163</v>
+        <v>-120095793.5905028</v>
       </c>
       <c r="F18">
-        <v>-27725069.51853085</v>
+        <v>-186061905</v>
       </c>
       <c r="G18">
-        <v>21871199.50010103</v>
+        <v>-119031180.8868944</v>
       </c>
       <c r="H18">
-        <v>11591247.158671208</v>
+        <v>-29669539.951694287</v>
       </c>
       <c r="I18">
-        <v>-45098291.72195329</v>
+        <v>23405114.527341653</v>
+      </c>
+      <c r="J18">
+        <v>12404187.857285557</v>
+      </c>
+      <c r="K18">
+        <v>-48261215.97651308</v>
       </c>
     </row>
     <row r="19">
@@ -4064,51 +4697,57 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>110019499</v>
+        <v>224451596</v>
       </c>
       <c r="C20">
-        <v>187164875.82244077</v>
+        <v>117735608.16012198</v>
       </c>
       <c r="D20">
-        <v>144672713.62206912</v>
+        <v>200291499.97464335</v>
       </c>
       <c r="E20">
-        <v>101142652</v>
+        <v>154819191.8458879</v>
       </c>
       <c r="F20">
-        <v>119747632.77537872</v>
+        <v>59959847</v>
       </c>
       <c r="G20">
-        <v>61522642.00717727</v>
+        <v>108236192.2421368</v>
       </c>
       <c r="H20">
-        <v>-25113237.609928653</v>
+        <v>128146015.01270397</v>
       </c>
       <c r="I20">
-        <v>202650233.77855754</v>
+        <v>65837471.886074334</v>
+      </c>
+      <c r="J20">
+        <v>-26874529.785620984</v>
+      </c>
+      <c r="K20">
+        <v>216862908.25328487</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>-9350495.169314744</v>
-      </c>
       <c r="D21">
-        <v>14860959.782427922</v>
-      </c>
-      <c r="F21">
-        <v>-109873840.707465</v>
-      </c>
-      <c r="G21">
-        <v>-82049498.81527774</v>
+        <v>-10006282.934969138</v>
+      </c>
+      <c r="E21">
+        <v>15903218.55426069</v>
       </c>
       <c r="H21">
-        <v>-124780301.84089907</v>
+        <v>-117579734.26675719</v>
       </c>
       <c r="I21">
-        <v>-1134552815.4747443</v>
+        <v>-87803959.5712932</v>
+      </c>
+      <c r="J21">
+        <v>-133531645.36444435</v>
+      </c>
+      <c r="K21">
+        <v>-1214123559.3128603</v>
       </c>
     </row>
     <row r="22">
@@ -4116,28 +4755,34 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>-2705560</v>
+        <v>14612138</v>
       </c>
       <c r="C22">
-        <v>-2899075.074171782</v>
+        <v>-2895311.784810978</v>
       </c>
       <c r="D22">
-        <v>-2854832.6059814394</v>
+        <v>-3102398.8480393416</v>
       </c>
       <c r="E22">
+        <v>-3055053.4779345854</v>
+      </c>
+      <c r="F22">
+        <v>-2910602</v>
+      </c>
+      <c r="G22">
         <v>0</v>
       </c>
-      <c r="F22">
-        <v>-1354943.057529163</v>
-      </c>
-      <c r="G22">
-        <v>-7559187.454066315</v>
-      </c>
       <c r="H22">
-        <v>-3004580.238272901</v>
+        <v>-1449970.653843199</v>
       </c>
       <c r="I22">
-        <v>-11977028.716395313</v>
+        <v>-8089343.618087751</v>
+      </c>
+      <c r="J22">
+        <v>-3215303.512870425</v>
+      </c>
+      <c r="K22">
+        <v>-12817025.824449966</v>
       </c>
     </row>
     <row r="23">
@@ -4170,28 +4815,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-75877884</v>
+        <v>-87386976</v>
       </c>
       <c r="C28">
-        <v>-296608338.16809386</v>
+        <v>-81199504.63183975</v>
       </c>
       <c r="D28">
-        <v>-331728919.4666166</v>
+        <v>-317410671.71723485</v>
       </c>
       <c r="E28">
-        <v>-260318906</v>
+        <v>-354994400.3808109</v>
       </c>
       <c r="F28">
-        <v>-160544343.92414063</v>
+        <v>-364434664</v>
       </c>
       <c r="G28">
-        <v>-288028647.9234405</v>
+        <v>-278576115.9800194</v>
       </c>
       <c r="H28">
-        <v>1117006696.0605373</v>
+        <v>-171803963.30087343</v>
       </c>
       <c r="I28">
-        <v>1684685516.0339513</v>
+        <v>-308229253.35084397</v>
+      </c>
+      <c r="J28">
+        <v>1195346860.1017342</v>
+      </c>
+      <c r="K28">
+        <v>1802839274.779884</v>
       </c>
     </row>
     <row r="29">
@@ -4209,28 +4860,34 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-17330087</v>
+        <v>24906327</v>
       </c>
       <c r="C31">
-        <v>-196919348.0279407</v>
+        <v>-18545515.57640545</v>
       </c>
       <c r="D31">
-        <v>-36483571.74244352</v>
+        <v>-210730092.47719184</v>
       </c>
       <c r="E31">
-        <v>-65258803</v>
+        <v>-39042311.09932639</v>
       </c>
       <c r="F31">
-        <v>-64166834.026762515</v>
+        <v>-85595210</v>
       </c>
       <c r="G31">
-        <v>-159784252.70847812</v>
+        <v>-69835664.84888822</v>
       </c>
       <c r="H31">
-        <v>282333769.08245325</v>
+        <v>-68667111.70763005</v>
       </c>
       <c r="I31">
-        <v>1580866452.6983526</v>
+        <v>-170990563.83671853</v>
+      </c>
+      <c r="J31">
+        <v>302134969.7935098</v>
+      </c>
+      <c r="K31">
+        <v>1691738963.7301953</v>
       </c>
     </row>
     <row r="32">
@@ -4243,28 +4900,34 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1572033</v>
+        <v>-944773</v>
       </c>
       <c r="C33">
-        <v>6681598.674891217</v>
+        <v>-1682285.985530447</v>
       </c>
       <c r="D33">
-        <v>6598813.924687026</v>
+        <v>7150206.014573676</v>
       </c>
       <c r="E33">
-        <v>-802750</v>
+        <v>7061615.237481752</v>
       </c>
       <c r="F33">
-        <v>14874785.484961025</v>
+        <v>-13486937</v>
       </c>
       <c r="G33">
-        <v>-4994825.551503044</v>
+        <v>-859050.0803002013</v>
       </c>
       <c r="H33">
-        <v>35735040.46033006</v>
+        <v>15918013.908818483</v>
       </c>
       <c r="I33">
-        <v>1879184.1182400032</v>
+        <v>-5345132.720154702</v>
+      </c>
+      <c r="J33">
+        <v>38241282.31326999</v>
+      </c>
+      <c r="K33">
+        <v>2010978.8448121306</v>
       </c>
     </row>
     <row r="34">
@@ -4287,28 +4950,34 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>86817284</v>
+        <v>78236342</v>
       </c>
       <c r="C37">
-        <v>-229848324.38633758</v>
+        <v>92906128.67224589</v>
       </c>
       <c r="D37">
-        <v>-174196002.6066929</v>
+        <v>-245968510.1475553</v>
       </c>
       <c r="E37">
-        <v>-71857808</v>
+        <v>-186413067.6141434</v>
       </c>
       <c r="F37">
-        <v>120203847.94630991</v>
+        <v>-195748308</v>
       </c>
       <c r="G37">
-        <v>136145181.18135276</v>
+        <v>-76897484.56256175</v>
       </c>
       <c r="H37">
-        <v>809075744.662193</v>
+        <v>128634226.38513948</v>
       </c>
       <c r="I37">
-        <v>-868520323.2755167</v>
+        <v>145693589.31962198</v>
+      </c>
+      <c r="J37">
+        <v>865819474.8315191</v>
+      </c>
+      <c r="K37">
+        <v>-929433140.3951286</v>
       </c>
     </row>
     <row r="38">
@@ -4321,28 +4990,34 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-136469925</v>
+        <v>-216585620</v>
       </c>
       <c r="C39">
-        <v>-52346822.33066676</v>
+        <v>-146041108.72601986</v>
       </c>
       <c r="D39">
-        <v>-82606403.70345517</v>
+        <v>-56018115.137489446</v>
       </c>
       <c r="E39">
-        <v>-51020698</v>
+        <v>-88399922.4350844</v>
       </c>
       <c r="F39">
-        <v>41744292.27190533</v>
+        <v>-139337298</v>
       </c>
       <c r="G39">
-        <v>69676514.03895989</v>
+        <v>-54598984.38352204</v>
       </c>
       <c r="H39">
-        <v>-66609167.92826712</v>
+        <v>44671987.079732604</v>
       </c>
       <c r="I39">
-        <v>101186861.51458079</v>
+        <v>74563207.69879365</v>
+      </c>
+      <c r="J39">
+        <v>-71280736.29088442</v>
+      </c>
+      <c r="K39">
+        <v>108283502.34746307</v>
       </c>
     </row>
     <row r="40">
@@ -4350,28 +5025,34 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>25778709</v>
+        <v>67961820</v>
       </c>
       <c r="C40">
-        <v>135280863.49200168</v>
+        <v>27586673.35594584</v>
       </c>
       <c r="D40">
-        <v>9854048.29563985</v>
+        <v>144768653.56074074</v>
       </c>
       <c r="E40">
-        <v>-56102742</v>
+        <v>10545152.263658019</v>
       </c>
       <c r="F40">
-        <v>-310938551.1946999</v>
+        <v>92383027</v>
       </c>
       <c r="G40">
-        <v>-346636985.0153876</v>
+        <v>-60037452.53212267</v>
       </c>
       <c r="H40">
-        <v>-145920957.5575818</v>
+        <v>-332745920.11489904</v>
       </c>
       <c r="I40">
-        <v>151137434.51843125</v>
+        <v>-370948028.41792387</v>
+      </c>
+      <c r="J40">
+        <v>-156154980.13992268</v>
+      </c>
+      <c r="K40">
+        <v>161737309.57262507</v>
       </c>
     </row>
     <row r="41">
@@ -4384,28 +5065,34 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>2208948</v>
+        <v>-6589293</v>
       </c>
       <c r="C42">
-        <v>2588976.142794127</v>
+        <v>2363870.39150292</v>
       </c>
       <c r="D42">
-        <v>-6479828.5905739255</v>
+        <v>2770551.4336500783</v>
       </c>
       <c r="E42">
-        <v>-2497182</v>
+        <v>-6934284.984196912</v>
       </c>
       <c r="F42">
-        <v>-1035931.8080350155</v>
+        <v>636408</v>
       </c>
       <c r="G42">
-        <v>-8631833.743103758</v>
+        <v>-2672319.3990958794</v>
       </c>
       <c r="H42">
-        <v>-6545333.41345582</v>
+        <v>-1108585.864687652</v>
       </c>
       <c r="I42">
-        <v>3862710.254482949</v>
+        <v>-9237218.897728147</v>
+      </c>
+      <c r="J42">
+        <v>-7004383.923289708</v>
+      </c>
+      <c r="K42">
+        <v>4133617.6322516208</v>
       </c>
     </row>
     <row r="43">
@@ -4418,28 +5105,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-10286476</v>
+        <v>-9192609</v>
       </c>
       <c r="C44">
-        <v>7090712.481167488</v>
+        <v>-11007907.85899233</v>
       </c>
       <c r="D44">
-        <v>-7206187.468967264</v>
+        <v>7588012.614553186</v>
       </c>
       <c r="E44">
-        <v>-7527304</v>
+        <v>-7711586.326844761</v>
       </c>
       <c r="F44">
-        <v>-209602.88841078355</v>
+        <v>5039</v>
       </c>
       <c r="G44">
-        <v>-344143.7885066892</v>
+        <v>-8055224.049385271</v>
       </c>
       <c r="H44">
-        <v>35449567.87382572</v>
+        <v>-224303.1804676895</v>
       </c>
       <c r="I44">
-        <v>42780445.26477075</v>
+        <v>-368279.97402863513</v>
+      </c>
+      <c r="J44">
+        <v>37935788.388187386</v>
+      </c>
+      <c r="K44">
+        <v>45780809.64183081</v>
       </c>
     </row>
     <row r="45">
@@ -4457,28 +5150,34 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>6335234</v>
+        <v>-5278923</v>
       </c>
       <c r="C47">
-        <v>31384703.4877329</v>
+        <v>6779549.394482175</v>
       </c>
       <c r="D47">
-        <v>-21155036.031924915</v>
+        <v>33585838.743487954</v>
       </c>
       <c r="E47">
-        <v>11842757</v>
+        <v>-22638723.63996107</v>
       </c>
       <c r="F47">
-        <v>31541124.0792858</v>
+        <v>-7180985</v>
       </c>
       <c r="G47">
-        <v>21384751.333993573</v>
+        <v>12673337.093523229</v>
       </c>
       <c r="H47">
-        <v>15674354.341372902</v>
+        <v>33753229.73910817</v>
       </c>
       <c r="I47">
-        <v>-80278029.50859877</v>
+        <v>22884549.798401766</v>
+      </c>
+      <c r="J47">
+        <v>16773659.73915939</v>
+      </c>
+      <c r="K47">
+        <v>-85908250.0102195</v>
       </c>
     </row>
     <row r="48">
@@ -4486,28 +5185,34 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-31359538</v>
+        <v>-19900247</v>
       </c>
       <c r="C48">
-        <v>-520697.7017362623</v>
+        <v>-33558908.29906847</v>
       </c>
       <c r="D48">
-        <v>-20054750.442463722</v>
+        <v>-557216.3220039444</v>
       </c>
       <c r="E48">
-        <v>-17094376</v>
+        <v>-21461270.604794715</v>
       </c>
       <c r="F48">
-        <v>7442527.311727526</v>
+        <v>-16110400</v>
       </c>
       <c r="G48">
-        <v>5156946.329232441</v>
+        <v>-18293273.217666563</v>
       </c>
       <c r="H48">
-        <v>157813678.5396671</v>
+        <v>7964501.631611302</v>
       </c>
       <c r="I48">
-        <v>-158910771.80478504</v>
+        <v>5518623.6788925035</v>
+      </c>
+      <c r="J48">
+        <v>168881785.3901852</v>
+      </c>
+      <c r="K48">
+        <v>-170055822.2104859</v>
       </c>
     </row>
     <row r="49">
@@ -4515,10 +5220,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>190568754</v>
-      </c>
-      <c r="E49">
-        <v>39173057</v>
+        <v>227530260</v>
+      </c>
+      <c r="C49">
+        <v>203934105.7943436</v>
+      </c>
+      <c r="F49">
+        <v>12427987</v>
+      </c>
+      <c r="G49">
+        <v>41920420.75547102</v>
       </c>
     </row>
     <row r="50">
@@ -4546,28 +5257,34 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-8737870</v>
+        <v>-53006671</v>
       </c>
       <c r="C54">
-        <v>-80988079.03191069</v>
+        <v>-9350691.903024254</v>
       </c>
       <c r="D54">
-        <v>-55713179.52024406</v>
+        <v>-86668098.1572369</v>
       </c>
       <c r="E54">
-        <v>-3835916</v>
+        <v>-59620568.471685074</v>
       </c>
       <c r="F54">
-        <v>-28410700.676735338</v>
+        <v>-20838036</v>
       </c>
       <c r="G54">
-        <v>-6190152.391869932</v>
+        <v>-4104944.1891308962</v>
       </c>
       <c r="H54">
-        <v>-59179455.03121629</v>
+        <v>-30403257.175626878</v>
       </c>
       <c r="I54">
-        <v>-31154481.991525013</v>
+        <v>-6624292.630714853</v>
+      </c>
+      <c r="J54">
+        <v>-63329947.80029712</v>
+      </c>
+      <c r="K54">
+        <v>-33339470.889480833</v>
       </c>
     </row>
     <row r="55">
@@ -4609,23 +5326,29 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-3103027.2953979517</v>
+      <c r="B62">
+        <v>-246983</v>
       </c>
       <c r="D62">
-        <v>-3012857.6128712785</v>
+        <v>-3320655.0573470285</v>
+      </c>
+      <c r="E62">
+        <v>-3224161.41298056</v>
       </c>
       <c r="F62">
-        <v>-443181.77226818295</v>
-      </c>
-      <c r="G62">
-        <v>-140122.24069188672</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>-8737770.27264526</v>
+        <v>-474263.88919908827</v>
       </c>
       <c r="I62">
-        <v>-1097494.919163202</v>
+        <v>-149949.5759803294</v>
+      </c>
+      <c r="J62">
+        <v>-9350585.18138975</v>
+      </c>
+      <c r="K62">
+        <v>-1174466.6439566636</v>
       </c>
     </row>
     <row r="63">
@@ -4649,28 +5372,34 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-32890099</v>
+        <v>-35647607</v>
       </c>
       <c r="C67">
-        <v>-52294481.85667085</v>
+        <v>-35196813.68674129</v>
       </c>
       <c r="D67">
-        <v>-39680513.45657637</v>
+        <v>-55962103.81592091</v>
       </c>
       <c r="E67">
-        <v>-9481867</v>
+        <v>-42463467.170632385</v>
       </c>
       <c r="F67">
-        <v>-105818162.64457706</v>
+        <v>-21044159</v>
       </c>
       <c r="G67">
-        <v>-80580031.53459291</v>
+        <v>-10146868.399558803</v>
       </c>
       <c r="H67">
-        <v>-244336195.9792935</v>
+        <v>-113239615.21898933</v>
       </c>
       <c r="I67">
-        <v>-382911814.39945704</v>
+        <v>-86231432.65074407</v>
+      </c>
+      <c r="J67">
+        <v>-261472474.33977926</v>
+      </c>
+      <c r="K67">
+        <v>-409766957.21924555</v>
       </c>
     </row>
     <row r="68">
@@ -4723,28 +5452,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>3924023</v>
+        <v>15510933</v>
       </c>
       <c r="C77">
-        <v>15578042.103008933</v>
+        <v>4199230.4867640445</v>
       </c>
       <c r="D77">
-        <v>15122293.511023458</v>
+        <v>16670592.73685424</v>
       </c>
       <c r="E77">
+        <v>16182880.666419078</v>
+      </c>
+      <c r="F77">
+        <v>8948119</v>
+      </c>
+      <c r="G77">
         <v>0</v>
       </c>
-      <c r="F77">
-        <v>27977499.732386228</v>
-      </c>
-      <c r="G77">
-        <v>25983492.07619519</v>
-      </c>
       <c r="H77">
-        <v>10250385.101588847</v>
+        <v>29939674.109878853</v>
       </c>
       <c r="I77">
-        <v>19588193.50518374</v>
+        <v>27805818.691417158</v>
+      </c>
+      <c r="J77">
+        <v>10969285.760981483</v>
+      </c>
+      <c r="K77">
+        <v>20961992.156417284</v>
       </c>
     </row>
     <row r="78">
@@ -4752,28 +5487,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-36814122</v>
+        <v>-51158540</v>
       </c>
       <c r="C78">
-        <v>-67872523.95967978</v>
+        <v>-39396044.173505336</v>
       </c>
       <c r="D78">
-        <v>-54802806.967599824</v>
+        <v>-72632696.55277516</v>
       </c>
       <c r="E78">
-        <v>-9481867</v>
+        <v>-58646347.83705146</v>
       </c>
       <c r="F78">
-        <v>-133795661.27654125</v>
+        <v>-29992278</v>
       </c>
       <c r="G78">
-        <v>-106563524.71121015</v>
+        <v>-10146868.399558803</v>
       </c>
       <c r="H78">
-        <v>-254586579.9804603</v>
+        <v>-143179288.15126914</v>
       </c>
       <c r="I78">
-        <v>-402500007.90464073</v>
+        <v>-114037252.51976028</v>
+      </c>
+      <c r="J78">
+        <v>-272441758.9231617</v>
+      </c>
+      <c r="K78">
+        <v>-430728949.37566274</v>
       </c>
     </row>
     <row r="79">
@@ -4887,28 +5628,34 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>645996796</v>
+        <v>571750134</v>
       </c>
       <c r="C101">
-        <v>-241694857.35406262</v>
+        <v>691303144.786637</v>
       </c>
       <c r="D101">
-        <v>-185363579.57631898</v>
+        <v>-258645888.0325795</v>
       </c>
       <c r="E101">
-        <v>-89503344</v>
+        <v>-198363871.5911175</v>
       </c>
       <c r="F101">
-        <v>389933858.34437245</v>
+        <v>-214108981</v>
       </c>
       <c r="G101">
-        <v>389933858.34437245</v>
+        <v>-95780572.84377022</v>
       </c>
       <c r="H101">
-        <v>-1124946363.2389302</v>
+        <v>417281485.29741573</v>
       </c>
       <c r="I101">
-        <v>-861787261.1629969</v>
+        <v>417281485.29741573</v>
+      </c>
+      <c r="J101">
+        <v>-1203843368.0147274</v>
+      </c>
+      <c r="K101">
+        <v>-922227861.6054351</v>
       </c>
     </row>
     <row r="102">
@@ -4926,9 +5673,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>781288165</v>
-      </c>
-      <c r="E104">
+        <v>835188621</v>
+      </c>
+      <c r="C104">
+        <v>836083040.6488283</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -4956,11 +5709,11 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="F109">
-        <v>373278220.25398207</v>
-      </c>
-      <c r="G109">
-        <v>429991464.4262309</v>
+      <c r="H109">
+        <v>399457720.44036067</v>
+      </c>
+      <c r="I109">
+        <v>460148492.1130549</v>
       </c>
     </row>
     <row r="110">
@@ -4968,22 +5721,28 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-156157874</v>
+        <v>-369985087</v>
       </c>
       <c r="C110">
-        <v>-189183955.49443206</v>
+        <v>-167109852.63059324</v>
       </c>
       <c r="D110">
-        <v>-148570561.4527686</v>
+        <v>-202452185.81002998</v>
       </c>
       <c r="E110">
-        <v>-91418811</v>
-      </c>
-      <c r="H110">
-        <v>-834514280.2327405</v>
-      </c>
-      <c r="I110">
-        <v>-593345227.6391102</v>
+        <v>-158990411.39364293</v>
+      </c>
+      <c r="F110">
+        <v>-199261920</v>
+      </c>
+      <c r="G110">
+        <v>-97830379.23450504</v>
+      </c>
+      <c r="J110">
+        <v>-893042117.0297109</v>
+      </c>
+      <c r="K110">
+        <v>-634958910.5563611</v>
       </c>
     </row>
     <row r="111">
@@ -5020,23 +5779,29 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>3986085.172120767</v>
+      <c r="B117">
+        <v>4412851</v>
       </c>
       <c r="D117">
-        <v>3986266.741757663</v>
+        <v>4265645.328176626</v>
+      </c>
+      <c r="E117">
+        <v>4265839.632021105</v>
       </c>
       <c r="F117">
-        <v>2998277.0208175033</v>
-      </c>
-      <c r="G117">
-        <v>2998275.9203954614</v>
+        <v>2150012</v>
       </c>
       <c r="H117">
-        <v>6257436.597193408</v>
+        <v>3208558.225469355</v>
       </c>
       <c r="I117">
-        <v>5310325.354261825</v>
+        <v>3208557.0478702975</v>
+      </c>
+      <c r="J117">
+        <v>6696295.747483545</v>
+      </c>
+      <c r="K117">
+        <v>5682759.790717927</v>
       </c>
     </row>
     <row r="118">
@@ -5044,28 +5809,34 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-30192165</v>
+        <v>-53369798</v>
       </c>
       <c r="C118">
-        <v>-136398565.46111837</v>
+        <v>-32309662.743926413</v>
       </c>
       <c r="D118">
-        <v>-104025252.71483578</v>
+        <v>-145964744.45618936</v>
       </c>
       <c r="E118">
-        <v>-29572774</v>
+        <v>-111320961.3178803</v>
       </c>
       <c r="F118">
-        <v>-138175796.57760817</v>
+        <v>-71367627</v>
       </c>
       <c r="G118">
-        <v>-104865932.23830706</v>
+        <v>-31646831.366427537</v>
       </c>
       <c r="H118">
-        <v>-162762802.46335238</v>
+        <v>-147866619.92592785</v>
       </c>
       <c r="I118">
-        <v>-228466087.56090578</v>
+        <v>-112220601.07140847</v>
+      </c>
+      <c r="J118">
+        <v>-174178011.24388498</v>
+      </c>
+      <c r="K118">
+        <v>-244489331.50429016</v>
       </c>
     </row>
     <row r="119">
@@ -5073,28 +5844,34 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>51058670</v>
+        <v>155503547</v>
       </c>
       <c r="C119">
-        <v>79901578.42936705</v>
+        <v>54639619.51232822</v>
       </c>
       <c r="D119">
-        <v>58652366.07826129</v>
+        <v>85505396.90546322</v>
       </c>
       <c r="E119">
-        <v>31488241</v>
+        <v>62765891.98296751</v>
       </c>
       <c r="F119">
-        <v>104370642.18109378</v>
+        <v>54370554</v>
       </c>
       <c r="G119">
-        <v>61810050.236053124</v>
+        <v>33696637.75716237</v>
       </c>
       <c r="H119">
-        <v>7109608.928469181</v>
+        <v>111690574.33404197</v>
       </c>
       <c r="I119">
-        <v>4382348.249792963</v>
+        <v>66145037.20789899</v>
+      </c>
+      <c r="J119">
+        <v>7608234.345567709</v>
+      </c>
+      <c r="K119">
+        <v>4689699.926363241</v>
       </c>
     </row>
     <row r="120">
@@ -5127,10 +5904,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>794937581</v>
-      </c>
-      <c r="E125">
-        <v>-63648070</v>
+        <v>710379133</v>
+      </c>
+      <c r="C125">
+        <v>850689744.991215</v>
+      </c>
+      <c r="F125">
+        <v>-243563189</v>
+      </c>
+      <c r="G125">
+        <v>-68111964.6769889</v>
       </c>
     </row>
     <row r="126">
@@ -5143,28 +5926,34 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>794937581</v>
+        <v>710379133</v>
       </c>
       <c r="C127">
-        <v>-166095247.9468677</v>
+        <v>850689744.991215</v>
       </c>
       <c r="D127">
-        <v>-266383368.36978602</v>
+        <v>-177744174.50792718</v>
       </c>
       <c r="E127">
-        <v>-63648070</v>
+        <v>-285065903.4427939</v>
       </c>
       <c r="F127">
-        <v>347561982.17696726</v>
+        <v>-243563189</v>
       </c>
       <c r="G127">
-        <v>236834156.74312368</v>
+        <v>-68111964.6769889</v>
       </c>
       <c r="H127">
-        <v>-106640095.37814432</v>
+        <v>371937899.344031</v>
       </c>
       <c r="I127">
-        <v>-127469307.44771434</v>
+        <v>253444286.97354203</v>
+      </c>
+      <c r="J127">
+        <v>-114119193.39497478</v>
+      </c>
+      <c r="K127">
+        <v>-136409241.73001564</v>
       </c>
     </row>
     <row r="128">
@@ -5172,10 +5961,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>352888972</v>
-      </c>
-      <c r="E128">
-        <v>518981148</v>
+        <v>377640878</v>
+      </c>
+      <c r="C128">
+        <v>377638492.34961754</v>
+      </c>
+      <c r="F128">
+        <v>555382886</v>
+      </c>
+      <c r="G128">
+        <v>555379379.4627103</v>
       </c>
     </row>
     <row r="129">
@@ -5183,22 +5978,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1115628631</v>
-      </c>
-      <c r="E129">
-        <v>269390569</v>
+        <v>1031070183</v>
+      </c>
+      <c r="C129">
+        <v>1193872145.805984</v>
+      </c>
+      <c r="F129">
+        <v>176834162</v>
+      </c>
+      <c r="G129">
+        <v>288284011.1262123</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5209,6 +6010,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5216,27 +6019,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -5250,16 +6059,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>181830884</v>
+        <v>-20306807.891319335</v>
       </c>
       <c r="C3">
-        <v>194598435.7949497</v>
+        <v>194583413.89131933</v>
+      </c>
+      <c r="D3">
+        <v>118257652.13695157</v>
       </c>
       <c r="E3">
-        <v>35337141</v>
+        <v>27016214.203621652</v>
       </c>
       <c r="F3">
-        <v>205952077.6255126</v>
+        <v>-46225525.566340126</v>
+      </c>
+      <c r="G3">
+        <v>37815476.566340126</v>
+      </c>
+      <c r="H3">
+        <v>196293044.80700767</v>
       </c>
     </row>
     <row r="4">
@@ -5267,16 +6085,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>52028005</v>
+        <v>-131345066.86746718</v>
       </c>
       <c r="C4">
-        <v>97257833.22532704</v>
+        <v>55676937.86746718</v>
+      </c>
+      <c r="D4">
+        <v>104078915.5304152</v>
       </c>
       <c r="E4">
-        <v>133279038</v>
+        <v>-73097116.26078936</v>
       </c>
       <c r="F4">
-        <v>70637984.68911484</v>
+        <v>119827944.98974329</v>
+      </c>
+      <c r="G4">
+        <v>142626432.0102567</v>
+      </c>
+      <c r="H4">
+        <v>75592110.14565991</v>
       </c>
     </row>
     <row r="5">
@@ -5284,16 +6111,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>214418633</v>
+        <v>161128692.44128385</v>
       </c>
       <c r="C5">
-        <v>62220021.271099955</v>
+        <v>229456672.55871615</v>
+      </c>
+      <c r="D5">
+        <v>66583761.157544255</v>
       </c>
       <c r="E5">
-        <v>166212925</v>
+        <v>69835030.84522197</v>
       </c>
       <c r="F5">
-        <v>7829787.836675793</v>
+        <v>-63461830.725233674</v>
+      </c>
+      <c r="G5">
+        <v>177870104.72523367</v>
+      </c>
+      <c r="H5">
+        <v>8378922.29190889</v>
       </c>
     </row>
     <row r="6">
@@ -5301,16 +6137,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>27981600</v>
+        <v>30985737.054278277</v>
       </c>
       <c r="C6">
-        <v>29737678.70891638</v>
+        <v>29944061.945721723</v>
+      </c>
+      <c r="D6">
+        <v>31823301.504623115</v>
       </c>
       <c r="E6">
-        <v>28412774</v>
+        <v>31975547.732756212</v>
       </c>
       <c r="F6">
-        <v>21550205.290087566</v>
+        <v>31184225.09062414</v>
+      </c>
+      <c r="G6">
+        <v>30405475.90937586</v>
+      </c>
+      <c r="H6">
+        <v>23061607.704684585</v>
       </c>
     </row>
     <row r="7">
@@ -5318,16 +6163,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>-3235692</v>
+        <v>-1976788.9297082294</v>
       </c>
       <c r="C7">
-        <v>4548337.010999269</v>
+        <v>-3462624.0702917706</v>
+      </c>
+      <c r="D7">
+        <v>4867330.145787979</v>
       </c>
       <c r="E7">
-        <v>-1633167</v>
+        <v>3383120.6258484237</v>
       </c>
       <c r="F7">
-        <v>477973.81596359424</v>
+        <v>-1032025.4416149002</v>
+      </c>
+      <c r="G7">
+        <v>-1747707.5583850998</v>
+      </c>
+      <c r="H7">
+        <v>511496.03859846666</v>
       </c>
     </row>
     <row r="8">
@@ -5335,16 +6189,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>7196396</v>
+        <v>86386.857150984</v>
       </c>
       <c r="C8">
-        <v>-221554.57220671233</v>
+        <v>7701108.142849016</v>
+      </c>
+      <c r="D8">
+        <v>-237093.0838306481</v>
       </c>
       <c r="E8">
-        <v>6961942</v>
+        <v>-73784.11945803277</v>
       </c>
       <c r="F8">
-        <v>497366.5536061381</v>
+        <v>-2733426.942566607</v>
+      </c>
+      <c r="G8">
+        <v>7450210.942566607</v>
+      </c>
+      <c r="H8">
+        <v>532248.8667879007</v>
       </c>
     </row>
     <row r="9">
@@ -5367,16 +6230,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-28299314</v>
+        <v>-70097826.49593197</v>
       </c>
       <c r="C12">
-        <v>19012780.61868538</v>
+        <v>-30284058.504068032</v>
+      </c>
+      <c r="D12">
+        <v>20346223.254078843</v>
       </c>
       <c r="E12">
-        <v>-12079086</v>
+        <v>34455359.45196322</v>
       </c>
       <c r="F12">
-        <v>-1704380.9764789268</v>
+        <v>16330987.795083199</v>
+      </c>
+      <c r="G12">
+        <v>-12926240.795083199</v>
+      </c>
+      <c r="H12">
+        <v>-1823916.0569372252</v>
       </c>
     </row>
     <row r="13">
@@ -5409,16 +6281,25 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
-        <v>52935542</v>
+        <v>83697949.91923428</v>
       </c>
       <c r="C18">
-        <v>-9093686.376155064</v>
+        <v>56648124.08076572</v>
+      </c>
+      <c r="D18">
+        <v>-9731463.110134974</v>
       </c>
       <c r="E18">
-        <v>-111230163</v>
+        <v>65966111.4094972</v>
       </c>
       <c r="F18">
-        <v>-49596269.018631876</v>
+        <v>-67030724.113105595</v>
+      </c>
+      <c r="G18">
+        <v>-119031180.8868944</v>
+      </c>
+      <c r="H18">
+        <v>-53074654.479035944</v>
       </c>
     </row>
     <row r="19">
@@ -5431,27 +6312,36 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>110019499</v>
+        <v>106715987.83987802</v>
       </c>
       <c r="C20">
-        <v>42492162.20037165</v>
+        <v>117735608.16012198</v>
+      </c>
+      <c r="D20">
+        <v>45472308.12875545</v>
       </c>
       <c r="E20">
-        <v>101142652</v>
+        <v>94859344.8458879</v>
       </c>
       <c r="F20">
-        <v>58224990.76820145</v>
+        <v>-48276345.242136806</v>
+      </c>
+      <c r="G20">
+        <v>108236192.2421368</v>
+      </c>
+      <c r="H20">
+        <v>62308543.126629636</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>-24211454.951742664</v>
-      </c>
-      <c r="F21">
-        <v>-27824341.892187253</v>
+      <c r="D21">
+        <v>-25909501.489229828</v>
+      </c>
+      <c r="H21">
+        <v>-29775774.695463985</v>
       </c>
     </row>
     <row r="22">
@@ -5459,16 +6349,25 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>-2705560</v>
+        <v>17507449.78481098</v>
       </c>
       <c r="C22">
-        <v>-44242.46819034265</v>
+        <v>-2895311.784810978</v>
+      </c>
+      <c r="D22">
+        <v>-47345.370104756206</v>
       </c>
       <c r="E22">
+        <v>-144451.47793458542</v>
+      </c>
+      <c r="F22">
+        <v>-2910602</v>
+      </c>
+      <c r="G22">
         <v>0</v>
       </c>
-      <c r="F22">
-        <v>6204244.396537151</v>
+      <c r="H22">
+        <v>6639372.964244552</v>
       </c>
     </row>
     <row r="23">
@@ -5501,16 +6400,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-75877884</v>
+        <v>-6187471.368160248</v>
       </c>
       <c r="C28">
-        <v>35120581.29852271</v>
+        <v>-81199504.63183975</v>
+      </c>
+      <c r="D28">
+        <v>37583728.66357607</v>
       </c>
       <c r="E28">
-        <v>-260318906</v>
+        <v>9440263.619189084</v>
       </c>
       <c r="F28">
-        <v>127484303.99929988</v>
+        <v>-85858548.01998061</v>
+      </c>
+      <c r="G28">
+        <v>-278576115.9800194</v>
+      </c>
+      <c r="H28">
+        <v>136425290.04997054</v>
       </c>
     </row>
     <row r="29">
@@ -5528,16 +6436,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-17330087</v>
+        <v>43451842.57640545</v>
       </c>
       <c r="C31">
-        <v>-160435776.2854972</v>
+        <v>-18545515.57640545</v>
+      </c>
+      <c r="D31">
+        <v>-171687781.37786543</v>
       </c>
       <c r="E31">
-        <v>-65258803</v>
+        <v>46552898.90067361</v>
       </c>
       <c r="F31">
-        <v>95617418.68171561</v>
+        <v>-15759545.151111782</v>
+      </c>
+      <c r="G31">
+        <v>-69835664.84888822</v>
+      </c>
+      <c r="H31">
+        <v>102323452.12908848</v>
       </c>
     </row>
     <row r="32">
@@ -5550,16 +6467,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1572033</v>
+        <v>737512.985530447</v>
       </c>
       <c r="C33">
-        <v>82784.75020419061</v>
+        <v>-1682285.985530447</v>
+      </c>
+      <c r="D33">
+        <v>88590.77709192317</v>
       </c>
       <c r="E33">
-        <v>-802750</v>
+        <v>20548552.23748175</v>
       </c>
       <c r="F33">
-        <v>19869611.03646407</v>
+        <v>-12627886.9196998</v>
+      </c>
+      <c r="G33">
+        <v>-859050.0803002013</v>
+      </c>
+      <c r="H33">
+        <v>21263146.628973186</v>
       </c>
     </row>
     <row r="34">
@@ -5582,16 +6508,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>86817284</v>
+        <v>-14669786.67224589</v>
       </c>
       <c r="C37">
-        <v>-55652321.77964467</v>
+        <v>92906128.67224589</v>
+      </c>
+      <c r="D37">
+        <v>-59555442.53341189</v>
       </c>
       <c r="E37">
-        <v>-71857808</v>
+        <v>9335240.385856599</v>
       </c>
       <c r="F37">
-        <v>-15941333.235042855</v>
+        <v>-118850823.43743825</v>
+      </c>
+      <c r="G37">
+        <v>-76897484.56256175</v>
+      </c>
+      <c r="H37">
+        <v>-17059362.9344825</v>
       </c>
     </row>
     <row r="38">
@@ -5604,16 +6539,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-136469925</v>
+        <v>-70544511.27398014</v>
       </c>
       <c r="C39">
-        <v>30259581.372788407</v>
+        <v>-146041108.72601986</v>
+      </c>
+      <c r="D39">
+        <v>32381807.297594957</v>
       </c>
       <c r="E39">
-        <v>-51020698</v>
+        <v>50937375.5649156</v>
       </c>
       <c r="F39">
-        <v>-27932221.767054558</v>
+        <v>-84738313.61647797</v>
+      </c>
+      <c r="G39">
+        <v>-54598984.38352204</v>
+      </c>
+      <c r="H39">
+        <v>-29891220.619061045</v>
       </c>
     </row>
     <row r="40">
@@ -5621,16 +6565,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>25778709</v>
+        <v>40375146.64405416</v>
       </c>
       <c r="C40">
-        <v>125426815.19636184</v>
+        <v>27586673.35594584</v>
+      </c>
+      <c r="D40">
+        <v>134223501.29708272</v>
       </c>
       <c r="E40">
-        <v>-56102742</v>
+        <v>-81837874.73634198</v>
       </c>
       <c r="F40">
-        <v>35698433.82068771</v>
+        <v>152420479.53212267</v>
+      </c>
+      <c r="G40">
+        <v>-60037452.53212267</v>
+      </c>
+      <c r="H40">
+        <v>38202108.30302483</v>
       </c>
     </row>
     <row r="41">
@@ -5643,16 +6596,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>2208948</v>
+        <v>-8953163.39150292</v>
       </c>
       <c r="C42">
-        <v>9068804.733368052</v>
+        <v>2363870.39150292</v>
+      </c>
+      <c r="D42">
+        <v>9704836.417846989</v>
       </c>
       <c r="E42">
-        <v>-2497182</v>
+        <v>-7570692.984196912</v>
       </c>
       <c r="F42">
-        <v>7595901.935068742</v>
+        <v>3308727.3990958794</v>
+      </c>
+      <c r="G42">
+        <v>-2672319.3990958794</v>
+      </c>
+      <c r="H42">
+        <v>8128633.033040495</v>
       </c>
     </row>
     <row r="43">
@@ -5665,16 +6627,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-10286476</v>
+        <v>1815298.8589923307</v>
       </c>
       <c r="C44">
-        <v>14296899.95013475</v>
+        <v>-11007907.85899233</v>
+      </c>
+      <c r="D44">
+        <v>15299598.941397946</v>
       </c>
       <c r="E44">
-        <v>-7527304</v>
+        <v>-7716625.326844761</v>
       </c>
       <c r="F44">
-        <v>134540.90009590564</v>
+        <v>8060263.049385271</v>
+      </c>
+      <c r="G44">
+        <v>-8055224.049385271</v>
+      </c>
+      <c r="H44">
+        <v>143976.79356094563</v>
       </c>
     </row>
     <row r="45">
@@ -5692,16 +6663,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>6335234</v>
+        <v>-12058472.394482175</v>
       </c>
       <c r="C47">
-        <v>52539739.51965781</v>
+        <v>6779549.394482175</v>
+      </c>
+      <c r="D47">
+        <v>56224562.383449025</v>
       </c>
       <c r="E47">
-        <v>11842757</v>
+        <v>-15457738.639961071</v>
       </c>
       <c r="F47">
-        <v>10156372.745292228</v>
+        <v>-19854322.093523227</v>
+      </c>
+      <c r="G47">
+        <v>12673337.093523229</v>
+      </c>
+      <c r="H47">
+        <v>10868679.940706402</v>
       </c>
     </row>
     <row r="48">
@@ -5709,16 +6689,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-31359538</v>
+        <v>13658661.299068473</v>
       </c>
       <c r="C48">
-        <v>19534052.74072746</v>
+        <v>-33558908.29906847</v>
+      </c>
+      <c r="D48">
+        <v>20904054.28279077</v>
       </c>
       <c r="E48">
-        <v>-17094376</v>
+        <v>-5350870.604794715</v>
       </c>
       <c r="F48">
-        <v>2285580.9824950844</v>
+        <v>2182873.2176665626</v>
+      </c>
+      <c r="G48">
+        <v>-18293273.217666563</v>
+      </c>
+      <c r="H48">
+        <v>2445877.952718798</v>
       </c>
     </row>
     <row r="49">
@@ -5726,10 +6715,16 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>190568754</v>
-      </c>
-      <c r="E49">
-        <v>39173057</v>
+        <v>23596154.20565641</v>
+      </c>
+      <c r="C49">
+        <v>203934105.7943436</v>
+      </c>
+      <c r="F49">
+        <v>-29492433.75547102</v>
+      </c>
+      <c r="G49">
+        <v>41920420.75547102</v>
       </c>
     </row>
     <row r="50">
@@ -5757,16 +6752,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-8737870</v>
+        <v>-43655979.096975744</v>
       </c>
       <c r="C54">
-        <v>-25274899.511666626</v>
+        <v>-9350691.903024254</v>
+      </c>
+      <c r="D54">
+        <v>-27047529.68555183</v>
       </c>
       <c r="E54">
-        <v>-3835916</v>
+        <v>-38782532.471685074</v>
       </c>
       <c r="F54">
-        <v>-22220548.284865405</v>
+        <v>-16733091.810869103</v>
+      </c>
+      <c r="G54">
+        <v>-4104944.1891308962</v>
+      </c>
+      <c r="H54">
+        <v>-23778964.544912025</v>
       </c>
     </row>
     <row r="55">
@@ -5808,11 +6812,14 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-90169.68252667319</v>
-      </c>
-      <c r="F62">
-        <v>-303059.5315762962</v>
+      <c r="D62">
+        <v>-96493.6443664683</v>
+      </c>
+      <c r="E62">
+        <v>-3224161.41298056</v>
+      </c>
+      <c r="H62">
+        <v>-324314.3132187589</v>
       </c>
     </row>
     <row r="63">
@@ -5836,16 +6843,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-32890099</v>
+        <v>-450793.3132587075</v>
       </c>
       <c r="C67">
-        <v>-12613968.40009448</v>
+        <v>-35196813.68674129</v>
+      </c>
+      <c r="D67">
+        <v>-13498636.645288527</v>
       </c>
       <c r="E67">
-        <v>-9481867</v>
+        <v>-21419308.170632385</v>
       </c>
       <c r="F67">
-        <v>-25238131.109984145</v>
+        <v>-10897290.600441197</v>
+      </c>
+      <c r="G67">
+        <v>-10146868.399558803</v>
+      </c>
+      <c r="H67">
+        <v>-27008182.568245262</v>
       </c>
     </row>
     <row r="68">
@@ -5898,16 +6914,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>3924023</v>
+        <v>11311702.513235956</v>
       </c>
       <c r="C77">
-        <v>455748.5919854753</v>
+        <v>4199230.4867640445</v>
+      </c>
+      <c r="D77">
+        <v>487712.07043516263</v>
       </c>
       <c r="E77">
+        <v>7234761.666419078</v>
+      </c>
+      <c r="F77">
+        <v>8948119</v>
+      </c>
+      <c r="G77">
         <v>0</v>
       </c>
-      <c r="F77">
-        <v>1994007.656191036</v>
+      <c r="H77">
+        <v>2133855.4184616953</v>
       </c>
     </row>
     <row r="78">
@@ -5915,16 +6940,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-36814122</v>
+        <v>-11762495.826494664</v>
       </c>
       <c r="C78">
-        <v>-13069716.992079958</v>
+        <v>-39396044.173505336</v>
+      </c>
+      <c r="D78">
+        <v>-13986348.7157237</v>
       </c>
       <c r="E78">
-        <v>-9481867</v>
+        <v>-28654069.83705146</v>
       </c>
       <c r="F78">
-        <v>-27232136.5653311</v>
+        <v>-19845409.600441195</v>
+      </c>
+      <c r="G78">
+        <v>-10146868.399558803</v>
+      </c>
+      <c r="H78">
+        <v>-29142035.631508857</v>
       </c>
     </row>
     <row r="79">
@@ -6038,15 +7072,24 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>645996796</v>
+        <v>-119553010.78663695</v>
       </c>
       <c r="C101">
-        <v>-56331277.77774364</v>
+        <v>691303144.786637</v>
+      </c>
+      <c r="D101">
+        <v>-60282016.44146201</v>
       </c>
       <c r="E101">
-        <v>-89503344</v>
+        <v>15745109.408882499</v>
       </c>
       <c r="F101">
+        <v>-118328408.15622978</v>
+      </c>
+      <c r="G101">
+        <v>-95780572.84377022</v>
+      </c>
+      <c r="H101">
         <v>0</v>
       </c>
     </row>
@@ -6065,9 +7108,15 @@
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B104">
-        <v>781288165</v>
-      </c>
-      <c r="E104">
+        <v>-894419.648828268</v>
+      </c>
+      <c r="C104">
+        <v>836083040.6488283</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
         <v>0</v>
       </c>
     </row>
@@ -6095,8 +7144,8 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="F109">
-        <v>-56713244.17224884</v>
+      <c r="H109">
+        <v>-60690771.672694206</v>
       </c>
     </row>
     <row r="110">
@@ -6104,13 +7153,22 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-156157874</v>
+        <v>-202875234.36940676</v>
       </c>
       <c r="C110">
-        <v>-40613394.04166347</v>
+        <v>-167109852.63059324</v>
+      </c>
+      <c r="D110">
+        <v>-43461774.41638705</v>
       </c>
       <c r="E110">
-        <v>-91418811</v>
+        <v>40271508.60635707</v>
+      </c>
+      <c r="F110">
+        <v>-101431540.76549496</v>
+      </c>
+      <c r="G110">
+        <v>-97830379.23450504</v>
       </c>
     </row>
     <row r="111">
@@ -6147,11 +7205,14 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>-181.56963689578697</v>
-      </c>
-      <c r="F117">
-        <v>1.1004220419563353</v>
+      <c r="D117">
+        <v>-194.30384447891265</v>
+      </c>
+      <c r="E117">
+        <v>2115827.632021105</v>
+      </c>
+      <c r="H117">
+        <v>1.1775990575551987</v>
       </c>
     </row>
     <row r="118">
@@ -6159,16 +7220,25 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-30192165</v>
+        <v>-21060135.256073587</v>
       </c>
       <c r="C118">
-        <v>-32373312.746282592</v>
+        <v>-32309662.743926413</v>
+      </c>
+      <c r="D118">
+        <v>-34643783.13830906</v>
       </c>
       <c r="E118">
-        <v>-29572774</v>
+        <v>-39953334.3178803</v>
       </c>
       <c r="F118">
-        <v>-33309864.33930111</v>
+        <v>-39720795.63357246</v>
+      </c>
+      <c r="G118">
+        <v>-31646831.366427537</v>
+      </c>
+      <c r="H118">
+        <v>-35646018.85451938</v>
       </c>
     </row>
     <row r="119">
@@ -6176,16 +7246,25 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>51058670</v>
+        <v>100863927.48767178</v>
       </c>
       <c r="C119">
-        <v>21249212.351105757</v>
+        <v>54639619.51232822</v>
+      </c>
+      <c r="D119">
+        <v>22739504.922495708</v>
       </c>
       <c r="E119">
-        <v>31488241</v>
+        <v>8395337.98296751</v>
       </c>
       <c r="F119">
-        <v>42560591.94504066</v>
+        <v>20673916.24283763</v>
+      </c>
+      <c r="G119">
+        <v>33696637.75716237</v>
+      </c>
+      <c r="H119">
+        <v>45545537.12614298</v>
       </c>
     </row>
     <row r="120">
@@ -6218,10 +7297,16 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>794937581</v>
-      </c>
-      <c r="E125">
-        <v>-63648070</v>
+        <v>-140310611.991215</v>
+      </c>
+      <c r="C125">
+        <v>850689744.991215</v>
+      </c>
+      <c r="F125">
+        <v>-175451224.3230111</v>
+      </c>
+      <c r="G125">
+        <v>-68111964.6769889</v>
       </c>
     </row>
     <row r="126">
@@ -6234,16 +7319,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>794937581</v>
+        <v>-140310611.991215</v>
       </c>
       <c r="C127">
-        <v>100288120.42291832</v>
+        <v>850689744.991215</v>
+      </c>
+      <c r="D127">
+        <v>107321728.93486673</v>
       </c>
       <c r="E127">
-        <v>-63648070</v>
+        <v>-41502714.442793906</v>
       </c>
       <c r="F127">
-        <v>110727825.43384358</v>
+        <v>-175451224.3230111</v>
+      </c>
+      <c r="G127">
+        <v>-68111964.6769889</v>
+      </c>
+      <c r="H127">
+        <v>118493612.37048894</v>
       </c>
     </row>
     <row r="128">
@@ -6251,10 +7345,16 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>352888972</v>
-      </c>
-      <c r="E128">
-        <v>518981148</v>
+        <v>2385.6503824591637</v>
+      </c>
+      <c r="C128">
+        <v>377638492.34961754</v>
+      </c>
+      <c r="F128">
+        <v>3506.537289738655</v>
+      </c>
+      <c r="G128">
+        <v>555379379.4627103</v>
       </c>
     </row>
     <row r="129">
@@ -6262,22 +7362,28 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>1115628631</v>
-      </c>
-      <c r="E129">
-        <v>269390569</v>
+        <v>-162801962.80598402</v>
+      </c>
+      <c r="C129">
+        <v>1193872145.805984</v>
+      </c>
+      <c r="F129">
+        <v>-111449849.1262123</v>
+      </c>
+      <c r="G129">
+        <v>288284011.1262123</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:K129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -6288,6 +7394,8 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6295,27 +7403,33 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
         <v>2026/3</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
     </row>
@@ -6329,22 +7443,25 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>358478940.59117436</v>
+        <v>319550472.3405732</v>
       </c>
       <c r="C3">
-        <v>211985197.5911744</v>
+        <v>293631754.66555244</v>
       </c>
       <c r="D3">
-        <v>223338839.42173728</v>
-      </c>
-      <c r="F3">
-        <v>139762683.2918406</v>
+        <v>136863817.34057322</v>
+      </c>
+      <c r="E3">
+        <v>214899210.01062933</v>
       </c>
       <c r="H3">
-        <v>1330559689.143941</v>
-      </c>
-      <c r="I3">
-        <v>1149481746.12585</v>
+        <v>118687280.3114771</v>
+      </c>
+      <c r="J3">
+        <v>1423877181.9412189</v>
+      </c>
+      <c r="K3">
+        <v>1195585577.094665</v>
       </c>
     </row>
     <row r="4">
@@ -6352,22 +7469,25 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>192954040.60656482</v>
+        <v>-44686329.73037416</v>
       </c>
       <c r="C4">
-        <v>274205073.6065648</v>
+        <v>206486682.1268363</v>
       </c>
       <c r="D4">
-        <v>247585225.0703526</v>
-      </c>
-      <c r="F4">
-        <v>146104132.71023685</v>
+        <v>293436176.26962584</v>
+      </c>
+      <c r="E4">
+        <v>264949370.88487053</v>
       </c>
       <c r="H4">
-        <v>223448543.79634988</v>
-      </c>
-      <c r="I4">
-        <v>55626360.62283465</v>
+        <v>156351002.10142663</v>
+      </c>
+      <c r="J4">
+        <v>239119887.25159442</v>
+      </c>
+      <c r="K4">
+        <v>59527660.61644854</v>
       </c>
     </row>
     <row r="5">
@@ -6375,22 +7495,25 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>282594170.1527034</v>
+        <v>527004157.00276625</v>
       </c>
       <c r="C5">
-        <v>234388462.15270343</v>
+        <v>302413633.8362487</v>
       </c>
       <c r="D5">
-        <v>179998228.71827927</v>
-      </c>
-      <c r="F5">
-        <v>154202894.50574437</v>
+        <v>250827066.00276622</v>
+      </c>
+      <c r="E5">
+        <v>192622227.13713086</v>
       </c>
       <c r="H5">
-        <v>-9895550.712946124</v>
-      </c>
-      <c r="I5">
-        <v>-590830131.631358</v>
+        <v>165017762.5757498</v>
+      </c>
+      <c r="J5">
+        <v>-10589565.412109725</v>
+      </c>
+      <c r="K5">
+        <v>-632267420.76823</v>
       </c>
     </row>
     <row r="6">
@@ -6398,22 +7521,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>116739711.62273505</v>
+        <v>124728648.23737933</v>
       </c>
       <c r="C6">
-        <v>117170885.62273505</v>
+        <v>124927136.27372518</v>
       </c>
       <c r="D6">
-        <v>108983412.20390624</v>
-      </c>
-      <c r="F6">
-        <v>123890710.75851412</v>
+        <v>125388550.23737933</v>
+      </c>
+      <c r="E6">
+        <v>116626856.4374408</v>
       </c>
       <c r="H6">
-        <v>101116417.99757533</v>
-      </c>
-      <c r="I6">
-        <v>100863570.7237661</v>
+        <v>132579663.68801068</v>
+      </c>
+      <c r="J6">
+        <v>108208118.34380044</v>
+      </c>
+      <c r="K6">
+        <v>107937537.8755731</v>
       </c>
     </row>
     <row r="7">
@@ -6421,22 +7547,25 @@
         <v xml:space="preserve">    Değer Düşüklüğü (İptali) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B7">
-        <v>3509655.060150205</v>
+        <v>2811037.7716364022</v>
       </c>
       <c r="C7">
-        <v>5112180.060150205</v>
+        <v>3755801.259729732</v>
       </c>
       <c r="D7">
-        <v>1041816.8651145304</v>
-      </c>
-      <c r="F7">
-        <v>-13799743.577138597</v>
+        <v>5470717.771636402</v>
+      </c>
+      <c r="E7">
+        <v>1114883.6644468904</v>
       </c>
       <c r="H7">
-        <v>-12622041.096193086</v>
-      </c>
-      <c r="I7">
-        <v>80923624.01165666</v>
+        <v>-14767574.996030021</v>
+      </c>
+      <c r="J7">
+        <v>-13507275.511973979</v>
+      </c>
+      <c r="K7">
+        <v>86599122.6476449</v>
       </c>
     </row>
     <row r="8">
@@ -6444,22 +7573,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>4351608.240674811</v>
+        <v>7476617.796711319</v>
       </c>
       <c r="C8">
-        <v>4117154.2406748114</v>
+        <v>4656803.996993728</v>
       </c>
       <c r="D8">
-        <v>4836075.366487661</v>
-      </c>
-      <c r="F8">
-        <v>3732316.8450625665</v>
+        <v>4405906.796711319</v>
+      </c>
+      <c r="E8">
+        <v>5175248.747329868</v>
       </c>
       <c r="H8">
-        <v>-7472352.050326278</v>
-      </c>
-      <c r="I8">
-        <v>-2638848.37015029</v>
+        <v>3994079.2095382023</v>
+      </c>
+      <c r="J8">
+        <v>-7996418.098865354</v>
+      </c>
+      <c r="K8">
+        <v>-2823921.400532746</v>
       </c>
     </row>
     <row r="9">
@@ -6482,22 +7614,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>38171398.568729065</v>
+        <v>-45580302.293957934</v>
       </c>
       <c r="C12">
-        <v>54391626.568729065</v>
+        <v>40848511.99705723</v>
       </c>
       <c r="D12">
-        <v>33674464.97356476</v>
-      </c>
-      <c r="F12">
-        <v>59585830.98745258</v>
+        <v>58206329.706042066</v>
+      </c>
+      <c r="E12">
+        <v>36036190.395026</v>
       </c>
       <c r="H12">
-        <v>163987922.1300788</v>
-      </c>
-      <c r="I12">
-        <v>218999425.23832697</v>
+        <v>63764824.533821695</v>
+      </c>
+      <c r="J12">
+        <v>175489053.4713265</v>
+      </c>
+      <c r="K12">
+        <v>234358734.1472223</v>
       </c>
     </row>
     <row r="13">
@@ -6530,22 +7665,25 @@
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B18">
-        <v>42847015.081460044</v>
+        <v>196580722.29936224</v>
       </c>
       <c r="C18">
-        <v>-121318689.91853996</v>
+        <v>45852048.26702235</v>
       </c>
       <c r="D18">
-        <v>-161821272.56101677</v>
-      </c>
-      <c r="F18">
-        <v>-27725069.51853085</v>
+        <v>-129827256.70063777</v>
+      </c>
+      <c r="E18">
+        <v>-173170448.06953874</v>
       </c>
       <c r="H18">
-        <v>11591247.158671208</v>
-      </c>
-      <c r="I18">
-        <v>-45098291.72195329</v>
+        <v>-29669539.951694287</v>
+      </c>
+      <c r="J18">
+        <v>12404187.857285557</v>
+      </c>
+      <c r="K18">
+        <v>-48261215.97651308</v>
       </c>
     </row>
     <row r="19">
@@ -6558,42 +7696,45 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>196041722.82244077</v>
+        <v>364783248.97464335</v>
       </c>
       <c r="C20">
-        <v>187164875.82244077</v>
+        <v>209790915.89262852</v>
       </c>
       <c r="D20">
-        <v>202897704.39027056</v>
-      </c>
-      <c r="F20">
-        <v>119747632.77537872</v>
+        <v>200291499.97464335</v>
+      </c>
+      <c r="E20">
+        <v>217127734.97251755</v>
       </c>
       <c r="H20">
-        <v>-25113237.609928653</v>
-      </c>
-      <c r="I20">
-        <v>202650233.77855754</v>
+        <v>128146015.01270397</v>
+      </c>
+      <c r="J20">
+        <v>-26874529.785620984</v>
+      </c>
+      <c r="K20">
+        <v>216862908.25328487</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>-9350495.169314744</v>
-      </c>
       <c r="D21">
-        <v>-12963382.10975933</v>
-      </c>
-      <c r="F21">
-        <v>-109873840.707465</v>
+        <v>-10006282.934969138</v>
+      </c>
+      <c r="E21">
+        <v>-13872556.141203295</v>
       </c>
       <c r="H21">
-        <v>-124780301.84089907</v>
-      </c>
-      <c r="I21">
-        <v>-1134552815.4747443</v>
+        <v>-117579734.26675719</v>
+      </c>
+      <c r="J21">
+        <v>-133531645.36444435</v>
+      </c>
+      <c r="K21">
+        <v>-1214123559.3128603</v>
       </c>
     </row>
     <row r="22">
@@ -6601,22 +7742,25 @@
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B22">
-        <v>-5604635.074171782</v>
+        <v>14420341.151960658</v>
       </c>
       <c r="C22">
-        <v>-2899075.074171782</v>
+        <v>-5997710.632850319</v>
       </c>
       <c r="D22">
-        <v>3349411.790555712</v>
-      </c>
-      <c r="F22">
-        <v>-1354943.057529163</v>
+        <v>-3102398.8480393416</v>
+      </c>
+      <c r="E22">
+        <v>3584319.4863099665</v>
       </c>
       <c r="H22">
-        <v>-3004580.238272901</v>
-      </c>
-      <c r="I22">
-        <v>-11977028.716395313</v>
+        <v>-1449970.653843199</v>
+      </c>
+      <c r="J22">
+        <v>-3215303.512870425</v>
+      </c>
+      <c r="K22">
+        <v>-12817025.824449966</v>
       </c>
     </row>
     <row r="23">
@@ -6649,22 +7793,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-112167316.16809386</v>
+        <v>-40362983.71723485</v>
       </c>
       <c r="C28">
-        <v>-296608338.16809386</v>
+        <v>-120034060.36905521</v>
       </c>
       <c r="D28">
-        <v>-204244615.4673167</v>
-      </c>
-      <c r="F28">
-        <v>-160544343.92414063</v>
+        <v>-317410671.71723485</v>
+      </c>
+      <c r="E28">
+        <v>-218569110.33084038</v>
       </c>
       <c r="H28">
-        <v>1117006696.0605373</v>
-      </c>
-      <c r="I28">
-        <v>1684685516.0339513</v>
+        <v>-171803963.30087343</v>
+      </c>
+      <c r="J28">
+        <v>1195346860.1017342</v>
+      </c>
+      <c r="K28">
+        <v>1802839274.779884</v>
       </c>
     </row>
     <row r="29">
@@ -6682,22 +7829,25 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-148990632.0279407</v>
+        <v>-100228555.47719184</v>
       </c>
       <c r="C31">
-        <v>-196919348.0279407</v>
+        <v>-159439943.20470905</v>
       </c>
       <c r="D31">
-        <v>59133846.93927209</v>
-      </c>
-      <c r="F31">
-        <v>-64166834.026762515</v>
+        <v>-210730092.47719184</v>
+      </c>
+      <c r="E31">
+        <v>63281141.02976209</v>
       </c>
       <c r="H31">
-        <v>282333769.08245325</v>
-      </c>
-      <c r="I31">
-        <v>1580866452.6983526</v>
+        <v>-68667111.70763005</v>
+      </c>
+      <c r="J31">
+        <v>302134969.7935098</v>
+      </c>
+      <c r="K31">
+        <v>1691738963.7301953</v>
       </c>
     </row>
     <row r="32">
@@ -6710,22 +7860,25 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>5912315.674891217</v>
+        <v>19692370.014573675</v>
       </c>
       <c r="C33">
-        <v>6681598.674891217</v>
+        <v>6326970.10934343</v>
       </c>
       <c r="D33">
-        <v>26468424.961151093</v>
-      </c>
-      <c r="F33">
-        <v>14874785.484961025</v>
+        <v>7150206.014573676</v>
+      </c>
+      <c r="E33">
+        <v>28324761.866454937</v>
       </c>
       <c r="H33">
-        <v>35735040.46033006</v>
-      </c>
-      <c r="I33">
-        <v>1879184.1182400032</v>
+        <v>15918013.908818483</v>
+      </c>
+      <c r="J33">
+        <v>38241282.31326999</v>
+      </c>
+      <c r="K33">
+        <v>2010978.8448121306</v>
       </c>
     </row>
     <row r="34">
@@ -6748,22 +7901,25 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-71173232.38633758</v>
+        <v>28016139.85244471</v>
       </c>
       <c r="C37">
-        <v>-229848324.38633758</v>
+        <v>-76164896.91274765</v>
       </c>
       <c r="D37">
-        <v>-190137335.84173578</v>
-      </c>
-      <c r="F37">
-        <v>120203847.94630991</v>
+        <v>-245968510.1475553</v>
+      </c>
+      <c r="E37">
+        <v>-203472430.5486259</v>
       </c>
       <c r="H37">
-        <v>809075744.662193</v>
-      </c>
-      <c r="I37">
-        <v>-868520323.2755167</v>
+        <v>128634226.38513948</v>
+      </c>
+      <c r="J37">
+        <v>865819474.8315191</v>
+      </c>
+      <c r="K37">
+        <v>-929433140.3951286</v>
       </c>
     </row>
     <row r="38">
@@ -6776,22 +7932,25 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-137796049.33066675</v>
+        <v>-133266437.13748944</v>
       </c>
       <c r="C39">
-        <v>-52346822.33066676</v>
+        <v>-147460239.47998726</v>
       </c>
       <c r="D39">
-        <v>-110538625.47050972</v>
-      </c>
-      <c r="F39">
-        <v>41744292.27190533</v>
+        <v>-56018115.137489446</v>
+      </c>
+      <c r="E39">
+        <v>-118291143.05414546</v>
       </c>
       <c r="H39">
-        <v>-66609167.92826712</v>
-      </c>
-      <c r="I39">
-        <v>101186861.51458079</v>
+        <v>44671987.079732604</v>
+      </c>
+      <c r="J39">
+        <v>-71280736.29088442</v>
+      </c>
+      <c r="K39">
+        <v>108283502.34746307</v>
       </c>
     </row>
     <row r="40">
@@ -6799,22 +7958,25 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>217162314.49200168</v>
+        <v>120347446.56074074</v>
       </c>
       <c r="C40">
-        <v>135280863.49200168</v>
+        <v>232392779.44880927</v>
       </c>
       <c r="D40">
-        <v>45552482.11632756</v>
-      </c>
-      <c r="F40">
-        <v>-310938551.1946999</v>
+        <v>144768653.56074074</v>
+      </c>
+      <c r="E40">
+        <v>48747260.566682845</v>
       </c>
       <c r="H40">
-        <v>-145920957.5575818</v>
-      </c>
-      <c r="I40">
-        <v>151137434.51843125</v>
+        <v>-332745920.11489904</v>
+      </c>
+      <c r="J40">
+        <v>-156154980.13992268</v>
+      </c>
+      <c r="K40">
+        <v>161737309.57262507</v>
       </c>
     </row>
     <row r="41">
@@ -6827,22 +7989,25 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>7295106.142794127</v>
+        <v>-4455149.566349922</v>
       </c>
       <c r="C42">
-        <v>2588976.142794127</v>
+        <v>7806741.224248879</v>
       </c>
       <c r="D42">
-        <v>1116073.3444948168</v>
-      </c>
-      <c r="F42">
-        <v>-1035931.8080350155</v>
+        <v>2770551.4336500783</v>
+      </c>
+      <c r="E42">
+        <v>1194348.048843583</v>
       </c>
       <c r="H42">
-        <v>-6545333.41345582</v>
-      </c>
-      <c r="I42">
-        <v>3862710.254482949</v>
+        <v>-1108585.864687652</v>
+      </c>
+      <c r="J42">
+        <v>-7004383.923289708</v>
+      </c>
+      <c r="K42">
+        <v>4133617.6322516208</v>
       </c>
     </row>
     <row r="43">
@@ -6855,22 +8020,25 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>4331540.481167488</v>
+        <v>-1609635.385446814</v>
       </c>
       <c r="C44">
-        <v>7090712.481167488</v>
+        <v>4635328.804946126</v>
       </c>
       <c r="D44">
-        <v>-7071646.568871358</v>
-      </c>
-      <c r="F44">
-        <v>-209602.88841078355</v>
+        <v>7588012.614553186</v>
+      </c>
+      <c r="E44">
+        <v>-7567609.533283816</v>
       </c>
       <c r="H44">
-        <v>35449567.87382572</v>
-      </c>
-      <c r="I44">
-        <v>42780445.26477075</v>
+        <v>-224303.1804676895</v>
+      </c>
+      <c r="J44">
+        <v>37935788.388187386</v>
+      </c>
+      <c r="K44">
+        <v>45780809.64183081</v>
       </c>
     </row>
     <row r="45">
@@ -6888,22 +8056,25 @@
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
       <c r="B47">
-        <v>25877180.4877329</v>
+        <v>35487900.743487954</v>
       </c>
       <c r="C47">
-        <v>31384703.4877329</v>
+        <v>27692051.0444469</v>
       </c>
       <c r="D47">
-        <v>-10998663.286632687</v>
-      </c>
-      <c r="F47">
-        <v>31541124.0792858</v>
+        <v>33585838.743487954</v>
+      </c>
+      <c r="E47">
+        <v>-11770043.69925467</v>
       </c>
       <c r="H47">
-        <v>15674354.341372902</v>
-      </c>
-      <c r="I47">
-        <v>-80278029.50859877</v>
+        <v>33753229.73910817</v>
+      </c>
+      <c r="J47">
+        <v>16773659.73915939</v>
+      </c>
+      <c r="K47">
+        <v>-85908250.0102195</v>
       </c>
     </row>
     <row r="48">
@@ -6911,22 +8082,25 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-14785859.701736262</v>
+        <v>-4347063.322003944</v>
       </c>
       <c r="C48">
-        <v>-520697.7017362623</v>
+        <v>-15822851.403405856</v>
       </c>
       <c r="D48">
-        <v>-17769169.459968638</v>
-      </c>
-      <c r="F48">
-        <v>7442527.311727526</v>
+        <v>-557216.3220039444</v>
+      </c>
+      <c r="E48">
+        <v>-19015392.652075917</v>
       </c>
       <c r="H48">
-        <v>157813678.5396671</v>
-      </c>
-      <c r="I48">
-        <v>-158910771.80478504</v>
+        <v>7964501.631611302</v>
+      </c>
+      <c r="J48">
+        <v>168881785.3901852</v>
+      </c>
+      <c r="K48">
+        <v>-170055822.2104859</v>
       </c>
     </row>
     <row r="49">
@@ -6959,22 +8133,25 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-85890033.03191069</v>
+        <v>-118836733.1572369</v>
       </c>
       <c r="C54">
-        <v>-80988079.03191069</v>
+        <v>-91913845.87113026</v>
       </c>
       <c r="D54">
-        <v>-77933727.80510947</v>
-      </c>
-      <c r="F54">
-        <v>-28410700.676735338</v>
+        <v>-86668098.1572369</v>
+      </c>
+      <c r="E54">
+        <v>-83399533.01659709</v>
       </c>
       <c r="H54">
-        <v>-59179455.03121629</v>
-      </c>
-      <c r="I54">
-        <v>-31154481.991525013</v>
+        <v>-30403257.175626878</v>
+      </c>
+      <c r="J54">
+        <v>-63329947.80029712</v>
+      </c>
+      <c r="K54">
+        <v>-33339470.889480833</v>
       </c>
     </row>
     <row r="55">
@@ -7016,20 +8193,23 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-3103027.2953979517</v>
+      <c r="B62">
+        <v>-3567638.0573470285</v>
       </c>
       <c r="D62">
-        <v>-3315917.144447575</v>
-      </c>
-      <c r="F62">
-        <v>-443181.77226818295</v>
+        <v>-3320655.0573470285</v>
+      </c>
+      <c r="E62">
+        <v>-3548475.726199319</v>
       </c>
       <c r="H62">
-        <v>-8737770.27264526</v>
-      </c>
-      <c r="I62">
-        <v>-1097494.919163202</v>
+        <v>-474263.88919908827</v>
+      </c>
+      <c r="J62">
+        <v>-9350585.18138975</v>
+      </c>
+      <c r="K62">
+        <v>-1174466.6439566636</v>
       </c>
     </row>
     <row r="63">
@@ -7053,22 +8233,25 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-75702713.85667086</v>
+        <v>-70565551.81592092</v>
       </c>
       <c r="C67">
-        <v>-52294481.85667085</v>
+        <v>-81012049.1031034</v>
       </c>
       <c r="D67">
-        <v>-64918644.566560514</v>
-      </c>
-      <c r="F67">
-        <v>-105818162.64457706</v>
+        <v>-55962103.81592091</v>
+      </c>
+      <c r="E67">
+        <v>-69471649.73887765</v>
       </c>
       <c r="H67">
-        <v>-244336195.9792935</v>
-      </c>
-      <c r="I67">
-        <v>-382911814.39945704</v>
+        <v>-113239615.21898933</v>
+      </c>
+      <c r="J67">
+        <v>-261472474.33977926</v>
+      </c>
+      <c r="K67">
+        <v>-409766957.21924555</v>
       </c>
     </row>
     <row r="68">
@@ -7121,22 +8304,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>19502065.103008933</v>
+        <v>23233406.73685424</v>
       </c>
       <c r="C77">
-        <v>15578042.103008933</v>
+        <v>20869823.223618284</v>
       </c>
       <c r="D77">
-        <v>17116301.167214494</v>
-      </c>
-      <c r="F77">
-        <v>27977499.732386228</v>
+        <v>16670592.73685424</v>
+      </c>
+      <c r="E77">
+        <v>18316736.084880773</v>
       </c>
       <c r="H77">
-        <v>10250385.101588847</v>
-      </c>
-      <c r="I77">
-        <v>19588193.50518374</v>
+        <v>29939674.109878853</v>
+      </c>
+      <c r="J77">
+        <v>10969285.760981483</v>
+      </c>
+      <c r="K77">
+        <v>20961992.156417284</v>
       </c>
     </row>
     <row r="78">
@@ -7144,22 +8330,25 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-95204778.95967978</v>
+        <v>-93798958.55277516</v>
       </c>
       <c r="C78">
-        <v>-67872523.95967978</v>
+        <v>-101881872.3267217</v>
       </c>
       <c r="D78">
-        <v>-82034943.53293093</v>
-      </c>
-      <c r="F78">
-        <v>-133795661.27654125</v>
+        <v>-72632696.55277516</v>
+      </c>
+      <c r="E78">
+        <v>-87788383.46856031</v>
       </c>
       <c r="H78">
-        <v>-254586579.9804603</v>
-      </c>
-      <c r="I78">
-        <v>-402500007.90464073</v>
+        <v>-143179288.15126914</v>
+      </c>
+      <c r="J78">
+        <v>-272441758.9231617</v>
+      </c>
+      <c r="K78">
+        <v>-430728949.37566274</v>
       </c>
     </row>
     <row r="79">
@@ -7273,22 +8462,25 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>493805282.6459374</v>
+        <v>527213226.96742046</v>
       </c>
       <c r="C101">
-        <v>-241694857.35406262</v>
+        <v>528437829.5978277</v>
       </c>
       <c r="D101">
-        <v>-185363579.57631898</v>
-      </c>
-      <c r="F101">
-        <v>389933858.34437245</v>
+        <v>-258645888.0325795</v>
+      </c>
+      <c r="E101">
+        <v>-198363871.5911175</v>
       </c>
       <c r="H101">
-        <v>-1124946363.2389302</v>
-      </c>
-      <c r="I101">
-        <v>-861787261.1629969</v>
+        <v>417281485.29741573</v>
+      </c>
+      <c r="J101">
+        <v>-1203843368.0147274</v>
+      </c>
+      <c r="K101">
+        <v>-922227861.6054351</v>
       </c>
     </row>
     <row r="102">
@@ -7330,8 +8522,8 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="F109">
-        <v>373278220.25398207</v>
+      <c r="H109">
+        <v>399457720.44036067</v>
       </c>
     </row>
     <row r="110">
@@ -7339,16 +8531,19 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-253923018.49443206</v>
+        <v>-373175352.81003</v>
       </c>
       <c r="C110">
-        <v>-189183955.49443206</v>
-      </c>
-      <c r="H110">
-        <v>-834514280.2327405</v>
-      </c>
-      <c r="I110">
-        <v>-593345227.6391102</v>
+        <v>-271731659.20611817</v>
+      </c>
+      <c r="D110">
+        <v>-202452185.81002998</v>
+      </c>
+      <c r="J110">
+        <v>-893042117.0297109</v>
+      </c>
+      <c r="K110">
+        <v>-634958910.5563611</v>
       </c>
     </row>
     <row r="111">
@@ -7385,20 +8580,23 @@
       <c r="A117" t="str">
         <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
-      <c r="C117">
-        <v>3986085.172120767</v>
+      <c r="B117">
+        <v>6528484.328176626</v>
       </c>
       <c r="D117">
-        <v>3986267.842179705</v>
-      </c>
-      <c r="F117">
-        <v>2998277.0208175033</v>
+        <v>4265645.328176626</v>
+      </c>
+      <c r="E117">
+        <v>4265840.8096201625</v>
       </c>
       <c r="H117">
-        <v>6257436.597193408</v>
-      </c>
-      <c r="I117">
-        <v>5310325.354261825</v>
+        <v>3208558.225469355</v>
+      </c>
+      <c r="J117">
+        <v>6696295.747483545</v>
+      </c>
+      <c r="K117">
+        <v>5682759.790717927</v>
       </c>
     </row>
     <row r="118">
@@ -7406,22 +8604,25 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-137017956.46111837</v>
+        <v>-127966915.45618936</v>
       </c>
       <c r="C118">
-        <v>-136398565.46111837</v>
+        <v>-146627575.83368823</v>
       </c>
       <c r="D118">
-        <v>-137335117.05413687</v>
-      </c>
-      <c r="F118">
-        <v>-138175796.57760817</v>
+        <v>-145964744.45618936</v>
+      </c>
+      <c r="E118">
+        <v>-146966980.1723997</v>
       </c>
       <c r="H118">
-        <v>-162762802.46335238</v>
-      </c>
-      <c r="I118">
-        <v>-228466087.56090578</v>
+        <v>-147866619.92592785</v>
+      </c>
+      <c r="J118">
+        <v>-174178011.24388498</v>
+      </c>
+      <c r="K118">
+        <v>-244489331.50429016</v>
       </c>
     </row>
     <row r="119">
@@ -7429,22 +8630,25 @@
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
       <c r="B119">
-        <v>99472007.42936705</v>
+        <v>186638389.90546322</v>
       </c>
       <c r="C119">
-        <v>79901578.42936705</v>
+        <v>106448378.66062906</v>
       </c>
       <c r="D119">
-        <v>101212958.02330196</v>
-      </c>
-      <c r="F119">
-        <v>104370642.18109378</v>
+        <v>85505396.90546322</v>
+      </c>
+      <c r="E119">
+        <v>108311429.10911049</v>
       </c>
       <c r="H119">
-        <v>7109608.928469181</v>
-      </c>
-      <c r="I119">
-        <v>4382348.249792963</v>
+        <v>111690574.33404197</v>
+      </c>
+      <c r="J119">
+        <v>7608234.345567709</v>
+      </c>
+      <c r="K119">
+        <v>4689699.926363241</v>
       </c>
     </row>
     <row r="120">
@@ -7487,22 +8691,25 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>692490403.0531323</v>
+        <v>776198147.4920728</v>
       </c>
       <c r="C127">
-        <v>-166095247.9468677</v>
+        <v>741057535.1602767</v>
       </c>
       <c r="D127">
-        <v>-155655542.93594244</v>
-      </c>
-      <c r="F127">
-        <v>347561982.17696726</v>
+        <v>-177744174.50792718</v>
+      </c>
+      <c r="E127">
+        <v>-166572291.07230496</v>
       </c>
       <c r="H127">
-        <v>-106640095.37814432</v>
-      </c>
-      <c r="I127">
-        <v>-127469307.44771434</v>
+        <v>371937899.344031</v>
+      </c>
+      <c r="J127">
+        <v>-114119193.39497478</v>
+      </c>
+      <c r="K127">
+        <v>-136409241.73001564</v>
       </c>
     </row>
     <row r="128">
@@ -7517,7 +8724,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K129"/>
   </ignoredErrors>
 </worksheet>
 </file>